--- a/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
+++ b/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\IdeaProjects\OrangeHRM-Testing\docs\test-cases\members\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D976F7B-775C-4907-A886-7B2C8C160FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC5761-3207-479C-8090-CBC40704B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="692">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -142,15 +142,6 @@
     <t>Pre-condition</t>
   </si>
   <si>
-    <t>PIM_EMP</t>
-  </si>
-  <si>
-    <t>PIM_PERSONAL</t>
-  </si>
-  <si>
-    <t>PIM_JOB</t>
-  </si>
-  <si>
     <t>Req Level 1</t>
   </si>
   <si>
@@ -304,9 +295,6 @@
     <t>Sau run, điền actual result, Defect ID (nếu có), ảnh/log và ngày thực chạy tại sheet test case. Các tổng hợp tự cập nhật từ cột Result.</t>
   </si>
   <si>
-    <t>Giảng viên Trần Thị Thanh Nga</t>
-  </si>
-  <si>
     <t>Nguyễn Văn Thắng</t>
   </si>
   <si>
@@ -325,9 +313,6 @@
     <t>OrangeHRM Recruitment</t>
   </si>
   <si>
-    <t>Katalon Recorder (phần Recruitment của Nguyễn Văn Thắng)</t>
-  </si>
-  <si>
     <t>RECR_VAC, RECR_CAND, RECR_FLOW</t>
   </si>
   <si>
@@ -343,15 +328,6 @@
     <t>RECRUIT_VAC</t>
   </si>
   <si>
-    <t>RECR_VAC</t>
-  </si>
-  <si>
-    <t>RECR_CAND</t>
-  </si>
-  <si>
-    <t>RECR_FLOW</t>
-  </si>
-  <si>
     <t>Tạo vacancy, validation số lượng, Active/Publish, bộ lọc, sửa và hủy.</t>
   </si>
   <si>
@@ -379,20 +355,12 @@
     <t>Phân vùng tương đương / Autocomplete</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_01
-TC_RECRUIT_VAC_001, TC_RECRUIT_VAC_002, TC_RECRUIT_VAC_003, TC_RECRUIT_VAC_004, TC_RECRUIT_VAC_005, TC_RECRUIT_VAC_006, TC_RECRUIT_VAC_007</t>
-  </si>
-  <si>
     <t>Số vị trí tuyển</t>
   </si>
   <si>
     <t>Biên 0 và 1, số âm và dữ liệu không phải số; điều kiện cần xác nhận theo demo.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_02
-TC_RECRUIT_VAC_008, TC_RECRUIT_VAC_009, TC_RECRUIT_VAC_010, TC_RECRUIT_VAC_011</t>
-  </si>
-  <si>
     <t>Active / Publish</t>
   </si>
   <si>
@@ -402,10 +370,6 @@
     <t>Chuyển trạng thái</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_03
-TC_RECRUIT_VAC_012, TC_RECRUIT_VAC_013, TC_RECRUIT_VAC_014, TC_RECRUIT_VAC_015</t>
-  </si>
-  <si>
     <t>Lọc / Reset danh sách</t>
   </si>
   <si>
@@ -415,20 +379,12 @@
     <t>Bảng quyết định / Phân vùng tương đương</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_04
-TC_RECRUIT_VAC_016, TC_RECRUIT_VAC_017, TC_RECRUIT_VAC_018, TC_RECRUIT_VAC_019, TC_RECRUIT_VAC_020, TC_RECRUIT_VAC_021</t>
-  </si>
-  <si>
     <t>Sửa / hủy</t>
   </si>
   <si>
     <t>Thay mô tả, số lượng, manager; Cancel tạo/sửa; đảm bảo baseline không đổi.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_05
-TC_RECRUIT_VAC_022, TC_RECRUIT_VAC_023, TC_RECRUIT_VAC_024, TC_RECRUIT_VAC_025</t>
-  </si>
-  <si>
     <t>RECRUIT_CAND</t>
   </si>
   <si>
@@ -438,20 +394,12 @@
     <t>Tên, email, vacancy, consent; 3 trường bắt buộc và dữ liệu tối thiểu/đầy đủ.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_CAND_01
-TC_RECRUIT_CAND_001, TC_RECRUIT_CAND_002, TC_RECRUIT_CAND_003, TC_RECRUIT_CAND_004, TC_RECRUIT_CAND_005, TC_RECRUIT_CAND_006, TC_RECRUIT_CAND_007</t>
-  </si>
-  <si>
     <t>Email / contact</t>
   </si>
   <si>
     <t>Email hợp lệ/invalid; contact có và không hợp lệ; giữ số 0 đầu.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_CAND_02
-TC_RECRUIT_CAND_008, TC_RECRUIT_CAND_009, TC_RECRUIT_CAND_010, TC_RECRUIT_CAND_011, TC_RECRUIT_CAND_012</t>
-  </si>
-  <si>
     <t>CV &amp; file upload</t>
   </si>
   <si>
@@ -461,30 +409,18 @@
     <t>Giá trị biên / Chuyển trạng thái</t>
   </si>
   <si>
-    <t>TD_RECRUIT_CAND_03
-TC_RECRUIT_CAND_013, TC_RECRUIT_CAND_014, TC_RECRUIT_CAND_015, TC_RECRUIT_CAND_016, TC_RECRUIT_CAND_017</t>
-  </si>
-  <si>
     <t>Lọc ứng viên / Reset</t>
   </si>
   <si>
     <t>Vacancy, Candidate Name, Keywords, Date Range với AND, Reset.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_CAND_04
-TC_RECRUIT_CAND_018, TC_RECRUIT_CAND_019, TC_RECRUIT_CAND_020, TC_RECRUIT_CAND_021, TC_RECRUIT_CAND_022</t>
-  </si>
-  <si>
     <t>Sửa &amp; dữ liệu lưu</t>
   </si>
   <si>
     <t>Keywords/Notes, Cancel edit, đối chiếu hồ sơ sau reload.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_CAND_05
-TC_RECRUIT_CAND_023, TC_RECRUIT_CAND_024, TC_RECRUIT_CAND_025</t>
-  </si>
-  <si>
     <t>RECRUIT_FLOW</t>
   </si>
   <si>
@@ -494,10 +430,6 @@
     <t>Application Initiated→Shortlisted/Rejected; Reject từ Shortlisted; hủy Shortlist.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_01
-TC_RECRUIT_FLOW_001, TC_RECRUIT_FLOW_002, TC_RECRUIT_FLOW_003, TC_RECRUIT_FLOW_004, TC_RECRUIT_FLOW_005</t>
-  </si>
-  <si>
     <t>Lịch phỏng vấn / validation</t>
   </si>
   <si>
@@ -507,10 +439,6 @@
     <t>Phân vùng tương đương / Biên</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_02
-TC_RECRUIT_FLOW_006, TC_RECRUIT_FLOW_007, TC_RECRUIT_FLOW_008, TC_RECRUIT_FLOW_009, TC_RECRUIT_FLOW_010, TC_RECRUIT_FLOW_011, TC_RECRUIT_FLOW_012</t>
-  </si>
-  <si>
     <t>Interviewer</t>
   </si>
   <si>
@@ -520,36 +448,21 @@
     <t>Bảng quyết định / Autocomplete</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_03
-TC_RECRUIT_FLOW_013, TC_RECRUIT_FLOW_014, TC_RECRUIT_FLOW_015</t>
-  </si>
-  <si>
     <t>Hành động theo trạng thái</t>
   </si>
   <si>
     <t>Schedule không ở Initiated, có sau Shortlist, đổi khi Scheduled, terminal Rejected, Cancel Reject.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_04
-TC_RECRUIT_FLOW_016, TC_RECRUIT_FLOW_017, TC_RECRUIT_FLOW_018, TC_RECRUIT_FLOW_019, TC_RECRUIT_FLOW_020</t>
-  </si>
-  <si>
     <t>Detail / Candidate History</t>
   </si>
   <si>
     <t>Đối chiếu thông tin hồ sơ và chuỗi event khởi tạo/shortlist/reject/schedule.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_05
-TC_RECRUIT_FLOW_021, TC_RECRUIT_FLOW_022, TC_RECRUIT_FLOW_023, TC_RECRUIT_FLOW_024, TC_RECRUIT_FLOW_025</t>
-  </si>
-  <si>
     <t>Nguyễn Văn Thắng – 23130299</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_001</t>
-  </si>
-  <si>
     <t>Tạo vacancy với các trường bắt buộc</t>
   </si>
   <si>
@@ -559,298 +472,145 @@
     <t>Không phụ thuộc test case khác; fixture được thiết lập trước case và khôi phục sau case.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_01
-Positive; Phân vùng tương đương
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_002</t>
-  </si>
-  <si>
     <t>Tạo vacancy với đủ thông tin</t>
   </si>
   <si>
     <t>Tên, mô tả, số lượng, manager, Active và Publish giữ đúng giá trị đã lưu.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_003</t>
-  </si>
-  <si>
     <t>Không chọn Job Title</t>
   </si>
   <si>
     <t>Job Title hiện Required; VAC_RUN03 không được tạo.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_01
-Negative; Phân vùng tương đương
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_004</t>
-  </si>
-  <si>
     <t>Để trống Vacancy Name</t>
   </si>
   <si>
     <t>Vacancy Name hiện Required; không tạo vacancy.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_005</t>
-  </si>
-  <si>
     <t>Không chọn Hiring Manager</t>
   </si>
   <si>
     <t>Hiring Manager hiện Required; không lưu.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_006</t>
-  </si>
-  <si>
     <t>Tên vacancy chỉ có khoảng trắng</t>
   </si>
   <si>
     <t>Không tạo được vacancy chỉ có khoảng trắng; có lỗi bắt buộc/không hợp lệ.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_01
-Negative; Phân vùng tương đương
-Automation: P1
-Cần kiểm tra UI: Xác nhận trim trên demo trước khi cố định expected.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_007</t>
-  </si>
-  <si>
     <t>Hiring Manager từ autocomplete</t>
   </si>
   <si>
     <t>Lưu đúng nhân viên từ suggestion, không phải chuỗi tên tự do.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_01
-Positive; Phân vùng tương đương / Autocomplete
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_008</t>
-  </si>
-  <si>
     <t>Số vị trí tuyển bằng 1</t>
   </si>
   <si>
     <t>Chấp nhận giá trị 1; Positions=1 sau reload.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_02
-Positive; Phân tích giá trị biên
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_009</t>
-  </si>
-  <si>
     <t>Số vị trí tuyển bằng 0</t>
   </si>
   <si>
     <t>Không chấp nhận 0 nếu quy tắc số lượng phải dương; không tạo VAC_RUN09.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_02
-Negative; Phân tích giá trị biên
-Automation: P1
-Cần kiểm tra UI: Kiểm tra giới hạn số lượng của bản demo; cập nhật nếu 0 được phép.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_010</t>
-  </si>
-  <si>
     <t>Số vị trí tuyển âm</t>
   </si>
   <si>
     <t>Không lưu số âm; UI chặn hoặc hiển thị lỗi.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_02
-Negative; Phân tích giá trị biên
-Automation: P1
-Cần kiểm tra UI: Xác nhận có ràng buộc &gt;=1.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_011</t>
-  </si>
-  <si>
     <t>Số vị trí tuyển không phải số</t>
   </si>
   <si>
     <t>Chỉ chấp nhận số; chuỗi 'abc' bị chặn hoặc báo Invalid; không lưu 'abc'.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_02
-Negative; Phân tích giá trị biên
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_012</t>
-  </si>
-  <si>
     <t>Lưu vacancy Active</t>
   </si>
   <si>
     <t>Active bật và Publish tắt sau reload.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_03
-Positive; Chuyển trạng thái
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_013</t>
-  </si>
-  <si>
     <t>Lưu vacancy Inactive</t>
   </si>
   <si>
     <t>Active vẫn tắt sau reload.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_014</t>
-  </si>
-  <si>
     <t>Lưu vacancy bật Publish</t>
   </si>
   <si>
     <t>Hai checkbox giữ trạng thái On; không suy diễn về cổng tuyển dụng ngoài demo.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_015</t>
-  </si>
-  <si>
     <t>Đổi Active trên vacancy đã tồn tại</t>
   </si>
   <si>
     <t>Mỗi lần reload phản ánh trạng thái đã lưu; các trường khác không đổi.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_016</t>
-  </si>
-  <si>
     <t>Tìm vacancy theo Job Title</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_04
-Positive; Phân vùng tương đương
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_017</t>
-  </si>
-  <si>
     <t>Tìm vacancy theo Hiring Manager</t>
   </si>
   <si>
     <t>VAC_FILTER_A xuất hiện; các dòng có manager phù hợp.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_018</t>
-  </si>
-  <si>
     <t>Tìm vacancy theo Vacancy Name</t>
   </si>
   <si>
     <t>Có VAC_FILTER_A, không có VAC_FILTER_B.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_019</t>
-  </si>
-  <si>
     <t>Lọc kết hợp Job Title và Manager</t>
   </si>
   <si>
     <t>Chỉ có vacancy thỏa đồng thời hai điều kiện.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_04
-Positive; Bảng quyết định
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_020</t>
-  </si>
-  <si>
     <t>Lọc vacancy không tồn tại</t>
   </si>
   <si>
     <t>Không có kết quả hoặc hiển thị No Records Found; không hiện dữ liệu khác.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_04
-Negative; Phân vùng tương đương
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_021</t>
-  </si>
-  <si>
     <t>Reset điều kiện lọc vacancy</t>
   </si>
   <si>
     <t>Bộ lọc về mặc định; danh sách trở về trạng thái không lọc.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_04
-Positive; Chuyển trạng thái
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_022</t>
-  </si>
-  <si>
     <t>Sửa Description của vacancy</t>
   </si>
   <si>
     <t>Description mới được lưu chính xác; field còn lại giữ baseline.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_05
-Positive; Phân vùng tương đương
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_023</t>
-  </si>
-  <si>
     <t>Sửa Positions và Hiring Manager</t>
   </si>
   <si>
     <t>Positions=4 và Hiring Manager=MANAGER_B sau tải lại.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_VAC_024</t>
-  </si>
-  <si>
     <t>Hủy tạo vacancy</t>
   </si>
   <si>
     <t>Không tạo bản ghi VAC_CANCEL_RUN.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_VAC_05
-Positive; Chuyển trạng thái
-Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_VAC_025</t>
-  </si>
-  <si>
     <t>Hủy sửa vacancy giữ dữ liệu cũ</t>
   </si>
   <si>
     <t>Name và trường khác vẫn đúng baseline; không xuất hiện tên tạm.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_001</t>
   </si>
   <si>
     <t>Tạo ứng viên tối thiểu</t>
@@ -872,9 +632,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_002</t>
-  </si>
-  <si>
     <t>Tạo ứng viên với thông tin đầy đủ</t>
   </si>
   <si>
@@ -889,9 +646,6 @@
     <t>Lưu đúng tên đầy đủ, email, phone, vacancy, keyword và notes.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_003</t>
-  </si>
-  <si>
     <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
 Input: First rỗng; Last=NguyenRUN03; Email=run03@example.com
 1. Mở Add Candidate, nhập Last và Email; First để rỗng.
@@ -907,9 +661,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_004</t>
-  </si>
-  <si>
     <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
 Input: First=An; Last rỗng; Email=run04@example.com
 1. Mở Add Candidate, nhập First/Email; Last để rỗng.
@@ -920,9 +671,6 @@
     <t>Last Name báo Required; hồ sơ không được tạo.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_005</t>
-  </si>
-  <si>
     <t>Bỏ trống Email</t>
   </si>
   <si>
@@ -936,9 +684,6 @@
     <t>Email báo Required; hồ sơ không được tạo.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_006</t>
-  </si>
-  <si>
     <t>Không chọn Vacancy tùy chọn</t>
   </si>
   <si>
@@ -956,9 +701,6 @@
 Positive; Phân vùng tương đương
 Automation: P1
 Cần kiểm tra UI: Theo hướng dẫn OrangeHRM, Vacancy không đánh dấu bắt buộc; kiểm tra trên demo.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_007</t>
   </si>
   <si>
     <t>Kiểm tra consent khi tạo hồ sơ</t>
@@ -981,9 +723,6 @@
 Cần kiểm tra UI: Demo có thể chỉ hiển thị consent ở form riêng; điều chỉnh nếu UI khác.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_008</t>
-  </si>
-  <si>
     <t>Email hợp lệ dạng example.com</t>
   </si>
   <si>
@@ -1002,9 +741,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_009</t>
-  </si>
-  <si>
     <t>Email thiếu ký tự @</t>
   </si>
   <si>
@@ -1023,9 +759,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_010</t>
-  </si>
-  <si>
     <t>Email thiếu phần domain</t>
   </si>
   <si>
@@ -1036,9 +769,6 @@
 Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_011</t>
-  </si>
-  <si>
     <t>Số điện thoại dạng chữ</t>
   </si>
   <si>
@@ -1058,9 +788,6 @@
 Cần kiểm tra UI: Demo có thể cho phép Phone tự do; xác nhận quy tắc trước khi khóa kỳ vọng.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_012</t>
-  </si>
-  <si>
     <t>Số điện thoại hợp lệ</t>
   </si>
   <si>
@@ -1072,9 +799,6 @@
   </si>
   <si>
     <t>Contact Number giữ đúng '0900000012' và không mất số 0 đầu.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_013</t>
   </si>
   <si>
     <t>Tải lên CV PDF hợp lệ</t>
@@ -1096,9 +820,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_014</t>
-  </si>
-  <si>
     <t>Tải lên CV DOCX hợp lệ</t>
   </si>
   <si>
@@ -1113,9 +834,6 @@
     <t>CV DOCX được đính kèm và hiển thị đúng tên.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_015</t>
-  </si>
-  <si>
     <t>Tải CV định dạng không hợp lệ</t>
   </si>
   <si>
@@ -1134,9 +852,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_016</t>
-  </si>
-  <si>
     <t>Tải CV vượt dung lượng tối đa</t>
   </si>
   <si>
@@ -1154,9 +869,6 @@
 Negative; Phân tích giá trị biên
 Automation: P1
 Cần kiểm tra UI: CV_LIMIT lấy từ demo, không áp dụng mặc định 5MB của bản thương mại.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_017</t>
   </si>
   <si>
     <t>Hủy chọn CV trước lưu</t>
@@ -1178,9 +890,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_018</t>
-  </si>
-  <si>
     <t>Lọc ứng viên theo Vacancy</t>
   </si>
   <si>
@@ -1200,9 +909,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_019</t>
-  </si>
-  <si>
     <t>Lọc theo Candidate Name</t>
   </si>
   <si>
@@ -1216,9 +922,6 @@
     <t>Hiện CAND_FILTER_A, không lẫn CAND_FILTER_B khác tên.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_020</t>
-  </si>
-  <si>
     <t>Lọc ứng viên theo Keywords</t>
   </si>
   <si>
@@ -1229,9 +932,6 @@
   </si>
   <si>
     <t>Hiện ứng viên có keyword phù hợp, gồm CAND_FILTER_A.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_021</t>
   </si>
   <si>
     <t>Lọc kết hợp Vacancy và ngày ứng tuyển</t>
@@ -1253,9 +953,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_022</t>
-  </si>
-  <si>
     <t>Reset bộ lọc Candidates</t>
   </si>
   <si>
@@ -1275,9 +972,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_023</t>
-  </si>
-  <si>
     <t>Sửa Keywords và Notes hồ sơ</t>
   </si>
   <si>
@@ -1294,9 +988,6 @@
     <t>TD_RECRUIT_CAND_05
 Positive; Phân vùng tương đương
 Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_CAND_024</t>
   </si>
   <si>
     <t>Hủy chỉnh sửa hồ sơ ứng viên</t>
@@ -1318,9 +1009,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_CAND_025</t>
-  </si>
-  <si>
     <t>Đối chiếu dữ liệu hồ sơ sau tải lại</t>
   </si>
   <si>
@@ -1334,9 +1022,6 @@
     <t>Chi tiết và dòng danh sách nhất quán; không mất dữ liệu khi reload.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_001</t>
-  </si>
-  <si>
     <t>Kiểm tra trạng thái ứng viên mới</t>
   </si>
   <si>
@@ -1357,9 +1042,6 @@
     <t>TD_RECRUIT_FLOW_01
 Positive; Phân vùng tương đương
 Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_FLOW_002</t>
   </si>
   <si>
     <t>Shortlist ứng viên mới</t>
@@ -1381,9 +1063,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_003</t>
-  </si>
-  <si>
     <t>Reject ứng viên từ trạng thái ban đầu</t>
   </si>
   <si>
@@ -1398,9 +1077,6 @@
     <t>Status chuyển Rejected; Candidate History có sự kiện reject.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_004</t>
-  </si>
-  <si>
     <t>Reject ứng viên đã Shortlisted</t>
   </si>
   <si>
@@ -1415,9 +1091,6 @@
     <t>Trạng thái Rejected; lịch sử còn sự kiện shortlist cũ và thêm reject.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_005</t>
-  </si>
-  <si>
     <t>Hủy hộp thoại Shortlist</t>
   </si>
   <si>
@@ -1432,9 +1105,6 @@
     <t>Status vẫn Application Initiated; History không có sự kiện Shortlist mới.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_006</t>
-  </si>
-  <si>
     <t>Đặt lịch phỏng vấn với dữ liệu đầy đủ</t>
   </si>
   <si>
@@ -1454,9 +1124,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_007</t>
-  </si>
-  <si>
     <t>Bỏ trống Interview Title</t>
   </si>
   <si>
@@ -1475,9 +1142,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_008</t>
-  </si>
-  <si>
     <t>Bỏ trống Interviewer</t>
   </si>
   <si>
@@ -1491,9 +1155,6 @@
     <t>Interviewer hiển thị Required; không tạo lịch.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_009</t>
-  </si>
-  <si>
     <t>Bỏ trống ngày phỏng vấn</t>
   </si>
   <si>
@@ -1505,9 +1166,6 @@
   </si>
   <si>
     <t>Date hiển thị Required; không lưu lịch.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_FLOW_010</t>
   </si>
   <si>
     <t>Ngày phỏng vấn không tồn tại</t>
@@ -1529,9 +1187,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_011</t>
-  </si>
-  <si>
     <t>Thời gian sai định dạng</t>
   </si>
   <si>
@@ -1549,9 +1204,6 @@
 Negative; Phân vùng tương đương / Giá trị biên
 Automation: P1
 Cần kiểm tra UI: Kiểm tra giao diện Time có cho nhập tự do hay chỉ chọn giờ.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_FLOW_012</t>
   </si>
   <si>
     <t>Lưu ghi chú phỏng vấn</t>
@@ -1573,9 +1225,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_013</t>
-  </si>
-  <si>
     <t>Chọn interviewer qua autocomplete</t>
   </si>
   <si>
@@ -1595,9 +1244,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_014</t>
-  </si>
-  <si>
     <t>Chọn nhiều interviewer</t>
   </si>
   <si>
@@ -1618,9 +1264,6 @@
 Cần kiểm tra UI: Chỉ chạy nếu bản demo hỗ trợ multi-select; nếu không, ghi Blocked và phiên bản.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_015</t>
-  </si>
-  <si>
     <t>Không chọn interviewer đã xóa</t>
   </si>
   <si>
@@ -1640,9 +1283,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_016</t>
-  </si>
-  <si>
     <t>Schedule Interview không có ở trạng thái mới</t>
   </si>
   <si>
@@ -1659,9 +1299,6 @@
     <t>TD_RECRUIT_FLOW_04
 Positive; Chuyển trạng thái
 Automation: P1</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_FLOW_017</t>
   </si>
   <si>
     <t>Schedule Interview xuất hiện sau Shortlist</t>
@@ -1678,9 +1315,6 @@
     <t>Nút Schedule Interview khả dụng; mở được form lịch của đúng candidate.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_018</t>
-  </si>
-  <si>
     <t>Trạng thái sau khi đặt lịch</t>
   </si>
   <si>
@@ -1694,9 +1328,6 @@
     <t>Status là Interview Scheduled; không còn status Shortlisted.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_019</t>
-  </si>
-  <si>
     <t>Không tái Shortlist sau khi Reject</t>
   </si>
   <si>
@@ -1714,9 +1345,6 @@
 Positive; Chuyển trạng thái
 Automation: P1
 Cần kiểm tra UI: Ghi nhận flow nếu phiên bản hỗ trợ Re-activate ứng viên.</t>
-  </si>
-  <si>
-    <t>TC_RECRUIT_FLOW_020</t>
   </si>
   <si>
     <t>Hủy Reject không đổi trạng thái</t>
@@ -1733,9 +1361,6 @@
     <t>Vẫn Shortlisted; không thêm bản ghi Reject vào History.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_021</t>
-  </si>
-  <si>
     <t>Candidate Details chứa đúng bản ghi</t>
   </si>
   <si>
@@ -1754,9 +1379,6 @@
 Automation: P1</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_022</t>
-  </si>
-  <si>
     <t>History sau khi tạo ứng viên</t>
   </si>
   <si>
@@ -1770,9 +1392,6 @@
     <t>Có dữ liệu sự kiện khởi tạo/đính vacancy theo cơ chế bản demo; không có event interview/reject.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_023</t>
-  </si>
-  <si>
     <t>History sau Shortlist</t>
   </si>
   <si>
@@ -1786,9 +1405,6 @@
     <t>Có event Shortlist gắn với đúng ứng viên và trình tự sau khi tạo.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_024</t>
-  </si>
-  <si>
     <t>History sau Reject</t>
   </si>
   <si>
@@ -1802,9 +1418,6 @@
     <t>Có event Reject của đúng ứng viên; trạng thái Rejected phù hợp event.</t>
   </si>
   <si>
-    <t>TC_RECRUIT_FLOW_025</t>
-  </si>
-  <si>
     <t>History sau Schedule Interview</t>
   </si>
   <si>
@@ -1824,15 +1437,9 @@
     <t>RUN_ID</t>
   </si>
   <si>
-    <t>Mỗi run một token duy nhất, thay chuỗi RUN trong toàn bộ test; lưu timestamp.</t>
-  </si>
-  <si>
     <t>Chỉ xóa fixture với RUN_ID của nhóm mình.</t>
   </si>
   <si>
-    <t>Không dùng dữ liệu thật.</t>
-  </si>
-  <si>
     <t>Admin / quyền Recruitment</t>
   </si>
   <si>
@@ -1875,9 +1482,6 @@
     <t>Tạo bản ghi Active; lưu snapshot Name/Description/Positions/Manager trước khi test.</t>
   </si>
   <si>
-    <t>VAC_015,022–025</t>
-  </si>
-  <si>
     <t>Restore sau mỗi TC, riêng nhánh thử Active cần reset.</t>
   </si>
   <si>
@@ -1893,9 +1497,6 @@
     <t>Tạo Job Title=JOB_A, Manager=MANAGER_A.</t>
   </si>
   <si>
-    <t>VAC_016–021</t>
-  </si>
-  <si>
     <t>Xóa sau khi ghi evidence.</t>
   </si>
   <si>
@@ -1911,9 +1512,6 @@
     <t>Tạo Job Title khác hoặc Manager khác, Name khác A.</t>
   </si>
   <si>
-    <t>VAC_018–019</t>
-  </si>
-  <si>
     <t>Negative control.</t>
   </si>
   <si>
@@ -1926,9 +1524,6 @@
     <t>Tạo ứng viên có Vacancy=VAC_A; lưu snapshot name, contact, keyword và note.</t>
   </si>
   <si>
-    <t>CAND_023–025</t>
-  </si>
-  <si>
     <t>Khôi phục tất cả field sau từng TC.</t>
   </si>
   <si>
@@ -1944,9 +1539,6 @@
     <t>A gán VAC_A + run_keyword_a; B khác vacancy hoặc keyword; kiểm tra ngày tạo.</t>
   </si>
   <si>
-    <t>CAND_018–022</t>
-  </si>
-  <si>
     <t>Dọn dữ liệu của hai fixture sau run.</t>
   </si>
   <si>
@@ -1962,9 +1554,6 @@
     <t>Tạo candidate mới với email flow_new_x_[RUN_ID]@example.com cho từng nhánh.</t>
   </si>
   <si>
-    <t>FLOW_001–005,016,021–022</t>
-  </si>
-  <si>
     <t>Không tái dùng F_NEW đã bị Shortlisted/Rejected.</t>
   </si>
   <si>
@@ -1980,9 +1569,6 @@
     <t>Tạo mới theo RUN_ID; thực hiện Shortlist trong setup và assert status trước case.</t>
   </si>
   <si>
-    <t>FLOW_004,006–015,017–018,020,023</t>
-  </si>
-  <si>
     <t>Không dùng sau Reject hay Schedule nếu case cần Shortlisted.</t>
   </si>
   <si>
@@ -1998,9 +1584,6 @@
     <t>Tạo mới riêng; Reject trong setup, assert Rejected.</t>
   </si>
   <si>
-    <t>FLOW_019,024</t>
-  </si>
-  <si>
     <t>Không dùng để test Shortlist.</t>
   </si>
   <si>
@@ -2016,9 +1599,6 @@
     <t>Tạo mới; Shortlist→Schedule; lưu Title/Date/Interviewer thực tế.</t>
   </si>
   <si>
-    <t>FLOW_025</t>
-  </si>
-  <si>
     <t>Không làm lại lịch trừ khi có kế hoạch rollback.</t>
   </si>
   <si>
@@ -2034,9 +1614,6 @@
     <t>Chọn bằng autocomplete, xác nhận hai employee khác nhau và không Deleted.</t>
   </si>
   <si>
-    <t>FLOW_006–015,025</t>
-  </si>
-  <si>
     <t>Không sửa danh mục Employee của hệ thống.</t>
   </si>
   <si>
@@ -2046,15 +1623,9 @@
     <t>CV_LIMIT</t>
   </si>
   <si>
-    <t>Giới hạn file thực tế của demo</t>
-  </si>
-  <si>
     <t>Đọc hướng dẫn cạnh Select Resume; ghi nguyên văn MB/KiB, quy đổi sang byte trước khi tạo tệp.</t>
   </si>
   <si>
-    <t>CAND_013–017</t>
-  </si>
-  <si>
     <t>Xóa file cục bộ tạm sau run.</t>
   </si>
   <si>
@@ -2085,9 +1656,6 @@
     <t>Interview dùng ngày hợp lệ trong tương lai tại lúc chạy; filter From/To bám theo fixture.</t>
   </si>
   <si>
-    <t>FLOW_006–012; CAND_021</t>
-  </si>
-  <si>
     <t>Không để ngày động gây false failure.</t>
   </si>
   <si>
@@ -2140,168 +1708,6 @@
   </si>
   <si>
     <t>https://www.orangehrm.com/assets/Files/Advanced-Recruitment-User-Guide.pdf</t>
-  </si>
-  <si>
-    <t>Tiền kiểm</t>
-  </si>
-  <si>
-    <t>Login thành công; mở được 2 tab Recruitment.</t>
-  </si>
-  <si>
-    <t>Demo có thể reset và bản UI có thể khác tài liệu.</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Dữ liệu riêng</t>
-  </si>
-  <si>
-    <t>Lưu ID, email, baseline và ngày; kiểm tra không trùng.</t>
-  </si>
-  <si>
-    <t>Không sửa Job Title/Employee đang dùng chung.</t>
-  </si>
-  <si>
-    <t>Chọn công cụ</t>
-  </si>
-  <si>
-    <t>Chạy smoke mở Recruitment và truy cập cả 2 tab.</t>
-  </si>
-  <si>
-    <t>Chạy browser theo cùng phiên bản trong nhóm.</t>
-  </si>
-  <si>
-    <t>Cấu trúc repo</t>
-  </si>
-  <si>
-    <t>Tên mỗi test chứa TC_RECRUIT_*; trace từ testcase tới source.</t>
-  </si>
-  <si>
-    <t>Mỗi thành viên chỉ sửa thư mục/module được giao.</t>
-  </si>
-  <si>
-    <t>Page Objects</t>
-  </si>
-  <si>
-    <t>Locator bằng role/label/test-id; wait trạng thái UI; không lạm dụng sleep.</t>
-  </si>
-  <si>
-    <t>Tách methods thao tác với assertions.</t>
-  </si>
-  <si>
-    <t>Vacancies Smoke</t>
-  </si>
-  <si>
-    <t>Assert validation, persist sau reload, trạng thái checkbox và dòng filter.</t>
-  </si>
-  <si>
-    <t>Trước khi chạy biên 0/-1 cần xác nhận rule.</t>
-  </si>
-  <si>
-    <t>Candidates Smoke</t>
-  </si>
-  <si>
-    <t>Assert email/name, validation, upload file, filter/reset và dữ liệu sửa.</t>
-  </si>
-  <si>
-    <t>Đọc CV_LIMIT từ UI trước khi tạo oversize file.</t>
-  </si>
-  <si>
-    <t>Workflow Smoke</t>
-  </si>
-  <si>
-    <t>Assert status theo từng bước, Interview details và History.</t>
-  </si>
-  <si>
-    <t>Mỗi nhánh dùng candidate fixture độc lập.</t>
-  </si>
-  <si>
-    <t>Case cần xác minh</t>
-  </si>
-  <si>
-    <t>Ghi chính xác tên field, boundary, quyền và hành vi trên demo.</t>
-  </si>
-  <si>
-    <t>Nếu không hỗ trợ/không setup được: Blocked + lý do.</t>
-  </si>
-  <si>
-    <t>Đồng bộ và cô lập</t>
-  </si>
-  <si>
-    <t>Không dùng wait cố định quá dài; không dùng dữ liệu từ test trước.</t>
-  </si>
-  <si>
-    <t>Fixture cleanup trong afterEach hoặc lệnh reset.</t>
-  </si>
-  <si>
-    <t>Chạy &amp; report</t>
-  </si>
-  <si>
-    <t>Actual, result, date, environment, defect ID, evidence link được điền vào Excel.</t>
-  </si>
-  <si>
-    <t>Chưa có kết quả execution tại thời điểm lập plan.</t>
-  </si>
-  <si>
-    <t>Git &amp; nộp</t>
-  </si>
-  <si>
-    <t>Ảnh chứa branch, commit, push thành công, PR/merge; repo public và link mở được.</t>
-  </si>
-  <si>
-    <t>Không thể xác minh link GitHub khi chưa được nhóm cung cấp.</t>
-  </si>
-  <si>
-    <t>Regressions</t>
-  </si>
-  <si>
-    <t>Kết quả test report và fixture cleanup trọn vẹn.</t>
-  </si>
-  <si>
-    <t>Ghi log của từng lần chạy; không sửa báo cáo người khác.</t>
-  </si>
-  <si>
-    <t>Kiểm tra URL demo, tài khoản Admin, quyền Recruitment, browser/version và giới hạn upload.</t>
-  </si>
-  <si>
-    <t>Tạo RUN_ID; tạo JOB_A/MANAGER_A/B (hoặc chọn sẵn), VAC_A và fixture filter, CV giả.</t>
-  </si>
-  <si>
-    <t>Dùng Playwright (TypeScript/JavaScript) cho project chung; nếu nhóm chọn Katalon thì thống nhất một framework.</t>
-  </si>
-  <si>
-    <t>tests/recruitment/vacancies.spec.ts; candidates.spec.ts; workflow.spec.ts; pages/; fixtures/; evidence/.</t>
-  </si>
-  <si>
-    <t>Bọc locator cho Vacancies list/add/edit, Candidates list/detail, Schedule Interview, Candidate History.</t>
-  </si>
-  <si>
-    <t>Automate VAC_001, 003–005, 008, 012–014, 016–021, 022–025.</t>
-  </si>
-  <si>
-    <t>Automate CAND_001–005, 008–010, 013–016, 018–025.</t>
-  </si>
-  <si>
-    <t>Automate FLOW_001–009, 012–013, 016–018, 020–025.</t>
-  </si>
-  <si>
-    <t>Kiểm tra real UI trước khi chốt expected: VAC_006/009/010, CAND_006/007/011/016, FLOW_011/014/019.</t>
-  </si>
-  <si>
-    <t>Dùng expect().toBeVisible/toHaveText, auto-wait; chạy serial chỉ khi có ràng buộc thật.</t>
-  </si>
-  <si>
-    <t>npm ci → npx playwright test tests/recruitment → playwright show-report; lưu screenshot/trace khi fail.</t>
-  </si>
-  <si>
-    <t>Tạo nhánh feature/recruitment-[MaSV]; commit xlsx+plan; push; PR→dev, nhóm trưởng gộp.</t>
-  </si>
-  <si>
-    <t>Chạy lại suite sau merge; kiểm tra không ảnh hưởng test case của thành viên khác.</t>
-  </si>
-  <si>
-    <t>OrangeHRM Open Source Demo; Admin; trình duyệt và Katalon Recorder.</t>
   </si>
   <si>
     <t>Môi trường kiểm thử trực tiếp</t>
@@ -2512,6 +1918,703 @@
 1. Mở VAC_EDIT; chỉnh Positions=4, chọn NNLinhB201.
 2. Save rồi reload.
 Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>G01_23130299_R01 chỉ là mẫu. Trước execution chọn RUN_ID duy nhất; resolve từng tên/email fixture chứa RUN, RUN_ID hoặc [RUN_ID] vào ledger theo TC, không replace toàn cục hoặc đổi input negative.</t>
+  </si>
+  <si>
+    <t>Chưa xác minh. Chỉ dùng dữ liệu giả; chưa tạo fixture hoặc ghi timestamp execution.</t>
+  </si>
+  <si>
+    <t>Chưa xác minh – đọc giới hạn thực tế trên OrangeHRM Demo trước execution.</t>
+  </si>
+  <si>
+    <t>Tiền kiểm và extension</t>
+  </si>
+  <si>
+    <t>Khi bắt đầu automation: kiểm tra/cài Katalon Recorder browser extension; ghi phiên bản thực tế của extension và browser, URL và quyền Recruitment.</t>
+  </si>
+  <si>
+    <t>Xác minh extension hoạt động, mở được Vacancies/Candidates; lưu môi trường khi execution thật.</t>
+  </si>
+  <si>
+    <t>Chưa cài/chạy trong lần sửa workbook; không tự điền phiên bản hoặc ngày chạy.</t>
+  </si>
+  <si>
+    <t>Fixture riêng</t>
+  </si>
+  <si>
+    <t>Chuẩn bị RUN_ID và ledger theo Test Data; xác minh JOB_A, MANAGER_A/B, INT_A/B; sau đó chuẩn bị vacancy/candidate đúng trạng thái.</t>
+  </si>
+  <si>
+    <t>Ghi key, tên/email, baseline và status thực tế; kiểm tra tên không trùng trước từng case.</t>
+  </si>
+  <si>
+    <t>QA Engineer cần kiểm tra lại; không tự tạo hoặc sửa employee/danh mục dùng chung.</t>
+  </si>
+  <si>
+    <t>Suite và test case</t>
+  </si>
+  <si>
+    <t>Tạo suite riêng cho RECRUIT_VAC, RECRUIT_CAND, RECRUIT_FLOW; tên test case giữ đúng TC_RECRUIT_* hiện tại.</t>
+  </si>
+  <si>
+    <t>Đủ mapping TC–TD; chọn 3–5 smoke mỗi chức năng trước khi mở rộng.</t>
+  </si>
+  <si>
+    <t>Chưa đổi 75 TC ID hoặc 15 TD ID; đề xuất đổi ID chờ nhóm trưởng xác nhận.</t>
+  </si>
+  <si>
+    <t>Record và chỉnh bước</t>
+  </si>
+  <si>
+    <t>Record thao tác trên OrangeHRM Demo ở giai đoạn automation; chỉnh Command, Target, Value; dùng input từ ledger đã xác minh.</t>
+  </si>
+  <si>
+    <t>Mỗi thao tác có target đúng field/form/candidate; đối chiếu input, checkpoint và expected.</t>
+  </si>
+  <si>
+    <t>Không record/tạo dữ liệu trong lần sửa workbook; không coi chuỗi click/type hoàn tất là Passed.</t>
+  </si>
+  <si>
+    <t>Locator, dropdown, AJAX</t>
+  </si>
+  <si>
+    <t>Khảo sát DOM thực tế; kiểm tra CSS/XPath duy nhất. Job Title theo loại dropdown; manager/interviewer phải chọn suggestion đúng người.</t>
+  </si>
+  <si>
+    <t>Đợi suggestion và tập kết quả mới sau Search/Reset; kiểm tra positive/negative controls và pagination nếu cần.</t>
+  </si>
+  <si>
+    <t>Không dự đoán selector; không chọn option theo index hoặc chỉ gõ tên mà không chọn autocomplete.</t>
+  </si>
+  <si>
+    <t>Vacancies smoke</t>
+  </si>
+  <si>
+    <t>Lỗi Required đúng field; không phát sinh record sai; dữ liệu mở lại và filter mặc định đúng expected.</t>
+  </si>
+  <si>
+    <t>Fixture JOB_A/MANAGER_A, VAC_FILTER_A/B phải sẵn; biên 0/-1 chờ xác minh rule.</t>
+  </si>
+  <si>
+    <t>Candidates smoke</t>
+  </si>
+  <si>
+    <t>Tên/email/vacancy sau mở lại đúng; validation đúng field; không tạo hồ sơ invalid.</t>
+  </si>
+  <si>
+    <t>Xác minh cách tìm đúng candidate; nhóm upload CV thực hiện sau preflight file/browser.</t>
+  </si>
+  <si>
+    <t>Workflow smoke</t>
+  </si>
+  <si>
+    <t>Assert status, interview title/interviewer/date/time/notes và Candidate History đúng candidate.</t>
+  </si>
+  <si>
+    <t>Không lấy output TC trước làm setup ngầm; INT_A và định dạng ngày/giờ phải được xác minh.</t>
+  </si>
+  <si>
+    <t>Giới hạn cần xác minh</t>
+  </si>
+  <si>
+    <t>Chốt rule, control tìm kiếm, CV format/limit theo byte, capability upload/download và trạng thái theo UI.</t>
+  </si>
+  <si>
+    <t>Không đổi Expected chỉ để Passed; chưa thực thi giữ Untested; thiếu fixture/capability khi chạy ghi Blocked kèm lý do.</t>
+  </si>
+  <si>
+    <t>Wait và assertion</t>
+  </si>
+  <si>
+    <t>Bổ sung wait/assertion đúng Command được phiên bản Recorder hỗ trợ; ví dụ waitForElementPresent, assertText, assertValue sau kiểm tra dropdown Command.</t>
+  </si>
+  <si>
+    <t>Required tại đúng field; Save rồi mở lại; đợi dữ liệu cuối sau AJAX, không chỉ container tồn tại.</t>
+  </si>
+  <si>
+    <t>Giới hạn timeout hữu hạn; không dùng pause dài thay đồng bộ; không đưa command của công cụ khác vào Recorder.</t>
+  </si>
+  <si>
+    <t>Replay và evidence</t>
+  </si>
+  <si>
+    <t>Chạy lại từng case rồi Play Suite; lưu log nguyên bản, ảnh checkpoint/lỗi, actual và status thật tại evidence/executions/23130299/&lt;RunID&gt;/&lt;CaseID&gt;/.</t>
+  </si>
+  <si>
+    <t>Đối chiếu assertion trước khi điền Result, Test date, Note/evidence; giữ riêng run lỗi và rerun.</t>
+  </si>
+  <si>
+    <t>Hiện chưa có execution; không điền ngày/kết quả giả. Chạy lại suite khi thay đổi hoặc sau tích hợp.</t>
+  </si>
+  <si>
+    <t>Cleanup và khôi phục</t>
+  </si>
+  <si>
+    <t>Ghi evidence trước cleanup; restore baseline của fixture edit; dọn candidate trước vacancy, chỉ xử lý key/record thuộc RUN_ID của mình.</t>
+  </si>
+  <si>
+    <t>Kiểm tra từng record đã dọn hoặc còn cần dọn; lưu kết quả cleanup thực tế, không khẳng định chung đã xong.</t>
+  </si>
+  <si>
+    <t>Case dừng vì assertion có thể bỏ qua bước cleanup cuối; cần checklist riêng. Không xóa employee/danh mục mượn dùng.</t>
+  </si>
+  <si>
+    <t>Lưu suite và Git</t>
+  </si>
+  <si>
+    <t>Lưu tại automation/23130299/KatalonRecorder/ theo chức năng; native HTML nếu phiên bản hỗ trợ, import lại để kiểm tra; kèm README setup/run/reset.</t>
+  </si>
+  <si>
+    <t>Kiểm tra status trên NVThang; khi sẵn sàng mới commit/push nhánh cá nhân, PR vào dev, lưu ảnh push/merge thật.</t>
+  </si>
+  <si>
+    <t>Chưa tạo suite/thư mục hoặc thao tác Git trong lần sửa này. Group01.txt đã có link; không cần tạo lại nhánh.</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_04</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_05</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_06</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_07</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_08</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_09</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_10</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_11</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_12</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_13</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Create_14</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Update_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Search_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Search_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Search_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Filter_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Filter_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Reset_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Update_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Update_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_CancelCreate_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_CancelUpdate_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_04</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_05</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_06</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_07</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_08</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_09</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_10</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_11</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Create_12</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_04</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_05</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Filter_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Search_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Filter_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Filter_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Reset_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Update_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_CancelUpdate_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_VerifyDetails_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Status_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Shortlist_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Reject_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Reject_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_CancelShortlist_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_04</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_05</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_06</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_07</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_SelectInterviewer_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_SelectInterviewer_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_SelectInterviewer_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ValidateAction_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ValidateAction_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Status_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ValidateAction_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_CancelReject_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_VerifyDetails_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_History_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_History_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_History_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_History_04</t>
+  </si>
+  <si>
+    <t>Giảng viên Trần Thị Thanh Nga</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Update_01, RECRUIT_VAC_Update_02, RECRUIT_VAC_Update_03, RECRUIT_VAC_CancelCreate_01, RECRUIT_VAC_CancelUpdate_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Search_01, RECRUIT_VAC_Search_02, RECRUIT_VAC_Search_03, RECRUIT_VAC_Filter_01, RECRUIT_VAC_Filter_02, RECRUIT_VAC_Reset_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_Search_03, RECRUIT_VAC_Filter_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Update_01, RECRUIT_CAND_CancelUpdate_01, RECRUIT_CAND_VerifyDetails_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_Filter_01, RECRUIT_CAND_Search_01, RECRUIT_CAND_Filter_02, RECRUIT_CAND_Filter_03, RECRUIT_CAND_Reset_01</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Status_01, RECRUIT_FLOW_Shortlist_01, RECRUIT_FLOW_Reject_01, RECRUIT_FLOW_CancelShortlist_01, RECRUIT_FLOW_ValidateAction_01, RECRUIT_FLOW_VerifyDetails_01, RECRUIT_FLOW_History_01; RECRUIT_FLOW_Reject_02 dùng F_SHORT_04.</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_Reject_02, RECRUIT_FLOW_ScheduleInterview_01, RECRUIT_FLOW_ScheduleInterview_02, RECRUIT_FLOW_ScheduleInterview_03, RECRUIT_FLOW_ScheduleInterview_04, RECRUIT_FLOW_ScheduleInterview_05, RECRUIT_FLOW_ScheduleInterview_06, RECRUIT_FLOW_ScheduleInterview_07, RECRUIT_FLOW_SelectInterviewer_01, RECRUIT_FLOW_SelectInterviewer_02, RECRUIT_FLOW_SelectInterviewer_03, RECRUIT_FLOW_ValidateAction_02, RECRUIT_FLOW_Status_02, RECRUIT_FLOW_CancelReject_01, RECRUIT_FLOW_History_02</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ValidateAction_03, RECRUIT_FLOW_History_03</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_01, RECRUIT_FLOW_ScheduleInterview_02, RECRUIT_FLOW_ScheduleInterview_03, RECRUIT_FLOW_ScheduleInterview_04, RECRUIT_FLOW_ScheduleInterview_05, RECRUIT_FLOW_ScheduleInterview_06, RECRUIT_FLOW_ScheduleInterview_07, RECRUIT_FLOW_SelectInterviewer_01, RECRUIT_FLOW_SelectInterviewer_02, RECRUIT_FLOW_SelectInterviewer_03, RECRUIT_FLOW_History_04</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND_UploadCV_01, RECRUIT_CAND_UploadCV_02, RECRUIT_CAND_UploadCV_03, RECRUIT_CAND_UploadCV_04, RECRUIT_CAND_UploadCV_05</t>
+  </si>
+  <si>
+    <t>RECRUIT_FLOW_ScheduleInterview_01, RECRUIT_FLOW_ScheduleInterview_02, RECRUIT_FLOW_ScheduleInterview_03, RECRUIT_FLOW_ScheduleInterview_04, RECRUIT_FLOW_ScheduleInterview_05, RECRUIT_FLOW_ScheduleInterview_06, RECRUIT_FLOW_ScheduleInterview_07; RECRUIT_CAND_Filter_03</t>
+  </si>
+  <si>
+    <t>Ưu tiên RECRUIT_VAC_Create_01, RECRUIT_VAC_Create_03, RECRUIT_VAC_Create_04, RECRUIT_VAC_Create_05, RECRUIT_VAC_Reset_01; record Required đơn giản trước, sau đó create/persist và Reset.</t>
+  </si>
+  <si>
+    <t>Ưu tiên RECRUIT_CAND_Create_01, RECRUIT_CAND_Create_03, RECRUIT_CAND_Create_04, RECRUIT_CAND_Create_05, RECRUIT_CAND_Create_09; chạy sau khi VAC_A được chuẩn bị và xác minh.</t>
+  </si>
+  <si>
+    <t>Ưu tiên RECRUIT_FLOW_Status_01, RECRUIT_FLOW_Shortlist_01, RECRUIT_FLOW_Reject_01, RECRUIT_FLOW_ScheduleInterview_01, RECRUIT_FLOW_ScheduleInterview_02; mỗi nhánh có F_NEW/F_SHORT riêng đúng trạng thái.</t>
+  </si>
+  <si>
+    <t>Review RECRUIT_VAC_Create_06, RECRUIT_VAC_Create_09, RECRUIT_VAC_Create_10, RECRUIT_VAC_Filter_02; RECRUIT_CAND_Create_06, RECRUIT_CAND_Create_07, RECRUIT_CAND_Create_11, RECRUIT_CAND_UploadCV_01, RECRUIT_CAND_UploadCV_02, RECRUIT_CAND_UploadCV_03, RECRUIT_CAND_UploadCV_04, RECRUIT_CAND_UploadCV_05; RECRUIT_FLOW_ScheduleInterview_06, RECRUIT_FLOW_SelectInterviewer_02, RECRUIT_FLOW_SelectInterviewer_03, RECRUIT_FLOW_ValidateAction_03, RECRUIT_FLOW_VerifyDetails_01 và các nhãn History còn điều kiện.</t>
+  </si>
+  <si>
+    <t>Kiểm thử tạo Vacancy với 7 trường hợp đầu tiên (Create_01–07), bao gồm các điều kiện nhập liệu và xác thực biểu mẫu.</t>
+  </si>
+  <si>
+    <t>Kiểm thử các trường hợp tạo Vacancy tiếp theo (Create_08–11), tập trung vào kiểm tra dữ liệu đầu vào.</t>
+  </si>
+  <si>
+    <t>Kiểm thử các trường hợp tạo Vacancy (Create_12–14) và cập nhật Vacancy (Update_01).</t>
+  </si>
+  <si>
+    <t>Kiểm thử tìm kiếm (Search_01–03), lọc (Filter_01–02) và đặt lại bộ lọc Vacancy (Reset_01).</t>
+  </si>
+  <si>
+    <t>Kiểm thử cập nhật Vacancy (Update_02–03), hủy tạo mới (CancelCreate_01) và hủy chỉnh sửa (CancelUpdate_01).</t>
+  </si>
+  <si>
+    <t>Kiểm thử thêm Candidate với 7 trường hợp đầu tiên (Create_01–07), bao gồm nhập thông tin và xác thực dữ liệu.</t>
+  </si>
+  <si>
+    <t>Kiểm thử các trường hợp thêm Candidate tiếp theo (Create_08–12), tập trung vào kiểm tra dữ liệu đầu vào.</t>
+  </si>
+  <si>
+    <t>Kiểm thử tải lên CV với 5 trường hợp (UploadCV_01–05), bao gồm các điều kiện kiểm tra tệp.</t>
+  </si>
+  <si>
+    <t>Kiểm thử lọc Candidate (Filter_01–03), tìm kiếm (Search_01) và đặt lại bộ lọc (Reset_01).</t>
+  </si>
+  <si>
+    <t>Kiểm thử cập nhật Candidate (Update_01), hủy chỉnh sửa (CancelUpdate_01) và xác minh thông tin chi tiết (VerifyDetails_01).</t>
+  </si>
+  <si>
+    <t>Kiểm thử trạng thái Candidate (Status_01), Shortlist, Reject (Reject_01–02) và hủy Shortlist.</t>
+  </si>
+  <si>
+    <t>Kiểm thử lên lịch phỏng vấn với 7 trường hợp (ScheduleInterview_01–07), bao gồm nhập liệu và xác thực lịch phỏng vấn.</t>
+  </si>
+  <si>
+    <t>Kiểm thử lựa chọn Interviewer với 3 trường hợp (SelectInterviewer_01–03).</t>
+  </si>
+  <si>
+    <t>Kiểm thử tính hợp lệ của thao tác Workflow (ValidateAction_01–03), thay đổi trạng thái (Status_02) và hủy Reject.</t>
+  </si>
+  <si>
+    <t>Kiểm thử thông tin chi tiết Candidate (VerifyDetails_01) và lịch sử xử lý hồ sơ (History_01–04).</t>
+  </si>
+  <si>
+    <t>Katalon Studio – Recruitment của Nguyễn Văn Thắng</t>
+  </si>
+  <si>
+    <t>OrangeHRM Open Source Demo; quyền Admin/Recruitment; Katalon Studio. Phiên bản Studio: Đã xác minh.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_01\20261023_115501_970</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_02\20261023_115554_453</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Negative; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_03\20261023_115632_409</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Negative; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_04\20261023_115648_301</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Negative; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_05\20261023_115705_926</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Negative; Phân vùng tương đương
+Automation: P1
+Cần kiểm tra UI: Xác nhận trim trên demo trước khi cố định expected.
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_06\20261023_115719_740</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_01
+Positive; Phân vùng tương đương / Autocomplete
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_07\20261023_115737_960</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_02
+Positive; Phân tích giá trị biên
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_08\20261023_115805_408</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Cần kiểm tra UI: Kiểm tra giới hạn số lượng của bản demo; cập nhật nếu 0 được phép.
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_09\20261023_115832_715</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Cần kiểm tra UI: Xác nhận có ràng buộc &gt;=1.
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_10\20261023_115853_350</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_11\20261023_115923_537</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_03
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_12\20261023_115952_922</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_03
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_13\20261023_120026_939</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_03
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Create_14\20261023_120057_775</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_03
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Update_01\20261023_120127_246</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Search_01\20261023_120214_025</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Search_02\20261023_120300_138</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Search_03\20261023_120351_395</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Positive; Bảng quyết định
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Filter_01\20261023_120426_216</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Negative; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Filter_02\20261023_120523_413</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_04
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_Reset_01\20261023_120602_233</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_05
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: ERROR (Katalon) – Timeout chờ toast Successfully Updated; không đủ bằng chứng xác nhận persistence.
+Ảnh: RECRUIT_VAC_Update_02\20261023_120736_956</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_05
+Positive; Phân vùng tương đương
+Automation: P1
+Run 20261023_115454: ERROR (Katalon) – Timeout chờ toast Successfully Updated; không đủ bằng chứng xác nhận persistence.
+Ảnh: RECRUIT_VAC_Update_03\20261023_120838_516</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_05
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_CancelCreate_01\20261023_121008_008</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_VAC_05
+Positive; Chuyển trạng thái
+Automation: P1
+Run 20261023_115454: PASSED theo execution report.
+Ảnh: RECRUIT_VAC_CancelUpdate_01\20261023_121027_749</t>
+  </si>
+  <si>
+    <t>Đã thực hiện Katalon Studio</t>
+  </si>
+  <si>
+    <t>Đã chuẩn bị RECRUIT_VAC</t>
+  </si>
+  <si>
+    <t>Đã tổ chức suite RECRUIT_VAC</t>
+  </si>
+  <si>
+    <t>Đã thực hiện RECRUIT_VAC</t>
+  </si>
+  <si>
+    <t>Chưa thực hiện RECRUIT_CAND</t>
+  </si>
+  <si>
+    <t>Chưa thực hiện RECRUIT_FLOW</t>
+  </si>
+  <si>
+    <t>Đã rà soát RECRUIT_VAC</t>
+  </si>
+  <si>
+    <t>Đã chạy RECRUIT_VAC</t>
+  </si>
+  <si>
+    <t>Đã lưu suite, Git xác nhận</t>
+  </si>
+  <si>
+    <t>Xác nhận cleanup dữ liệu</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Triển khai 25 test case bằng Katalon Studio 11.6; kết quả 23 Passed, 2 Error; bổ sung Test Report và Screenshot Evidence</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC Automation</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -2521,7 +2624,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2575,6 +2678,16 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2604,7 +2717,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2675,13 +2788,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF667085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF667085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF667085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF667085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF667085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2722,45 +2861,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2783,9 +2883,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2810,9 +2907,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2822,11 +2916,97 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="4" xr:uid="{0238528A-F37D-4FD9-878F-68D57738BE03}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{BA7E7360-1265-45E6-A2FE-F218883DFA75}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{0F7F3863-1CDF-4818-824C-BDB45FB4C1B1}"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -3169,7 +3349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H1000"/>
+  <dimension ref="B2:H1001"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3183,14 +3363,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
@@ -3206,16 +3386,16 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
       <c r="F4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -3223,39 +3403,41 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>87</v>
+        <v>620</v>
       </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="C6" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
       <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="33">
+        <v>46313</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3315,130 +3497,152 @@
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="2:8" ht="45.75" customHeight="1">
-      <c r="B12" s="5"/>
+      <c r="B12" s="5">
+        <v>46313</v>
+      </c>
       <c r="C12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+    <row r="13" spans="2:8" ht="65.400000000000006" customHeight="1">
+      <c r="B13" s="5">
+        <v>46318</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+    <row r="14" spans="2:8" ht="45.75" customHeight="1">
+      <c r="B14" s="37"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="2:8" ht="24.75" customHeight="1">
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="20">
-        <v>23130299</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
+    <row r="15" spans="2:8">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="2:8" ht="24.75" customHeight="1">
       <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="C16" s="49">
+        <v>23130299</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="51"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" ht="24.75" customHeight="1">
       <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+        <v>19</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" ht="24.75" customHeight="1">
       <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+        <v>21</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="2:8" ht="24.75" customHeight="1">
       <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="2:8" ht="36" customHeight="1">
+      <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:8" ht="24.75" customHeight="1">
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="38" t="s">
+        <v>651</v>
+      </c>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="2:8" ht="24.75" customHeight="1">
+      <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="C21" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="2:8" ht="15.75" customHeight="1"/>
+    <row r="22" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
     <row r="23" spans="2:8" ht="15.75" customHeight="1"/>
     <row r="24" spans="2:8" ht="15.75" customHeight="1"/>
     <row r="25" spans="2:8" ht="15.75" customHeight="1"/>
@@ -4417,19 +4621,20 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C17:G17"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:E7"/>
-    <mergeCell ref="C15:G15"/>
     <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4451,13 +4656,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
@@ -4471,43 +4676,43 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14" t="str">
+      <c r="C4" s="54"/>
+      <c r="D4" s="46" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="14" t="str">
+      <c r="C5" s="54"/>
+      <c r="D5" s="46" t="str">
         <f>Cover!C5</f>
         <v>Group01_OrangeHRM</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="2:8" ht="37.5" customHeight="1">
-      <c r="B6" s="28" t="s">
+    <row r="6" spans="2:8" ht="48" customHeight="1">
+      <c r="B6" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="28" t="s">
-        <v>641</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="41" t="s">
+        <v>652</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="57"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
@@ -4544,16 +4749,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -4563,16 +4768,16 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -4581,17 +4786,17 @@
       <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="29" t="s">
-        <v>98</v>
+      <c r="C11" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -4615,11 +4820,11 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="37.5" customHeight="1">
-      <c r="B14" s="22"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
@@ -4633,11 +4838,11 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B16" s="22"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
@@ -5671,352 +5876,352 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="73.5" customHeight="1">
-      <c r="A2" s="29" t="s">
-        <v>99</v>
+      <c r="A2" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>112</v>
+        <v>636</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="138" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>115</v>
+        <v>637</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="73.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>119</v>
+        <v>638</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="78" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>123</v>
+        <v>639</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="102" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>126</v>
+        <v>640</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="78" customHeight="1">
-      <c r="A7" s="29" t="s">
-        <v>127</v>
+      <c r="A7" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>130</v>
+        <v>641</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="102" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>642</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" ht="102" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>137</v>
+        <v>643</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" ht="78" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>140</v>
+        <v>644</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="90" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>143</v>
+        <v>645</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="73.5" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>144</v>
+      <c r="A12" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>147</v>
+        <v>646</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" ht="102" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>151</v>
+        <v>647</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" ht="73.5" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>155</v>
+        <v>648</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" ht="90" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>158</v>
+        <v>649</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" ht="138" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>161</v>
+        <v>650</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -7047,80 +7252,80 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+        <v>42</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="F5" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
         <f>COUNTIF($F$9:$F$33,"Passed")</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF($F$9:$F$33,"Failed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8">
         <f>COUNTIF($F$9:$F$33,"Untested")</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D6" s="8">
         <f>COUNTIF($F$9:$F$33,"Blocked")</f>
@@ -7130,12 +7335,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="59">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -7149,628 +7354,678 @@
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>163</v>
+        <v>545</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>650</v>
+        <v>140</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>468</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="9" t="s">
-        <v>167</v>
+        <v>142</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="139.5" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>168</v>
+        <v>546</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>651</v>
+        <v>143</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>469</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="9" t="s">
-        <v>167</v>
+        <v>142</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="139.5" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>171</v>
+        <v>547</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>652</v>
+        <v>470</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="9" t="s">
-        <v>174</v>
+        <v>142</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="139.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>175</v>
+        <v>548</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>653</v>
+        <v>471</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="9" t="s">
-        <v>174</v>
+        <v>142</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="139.5" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>178</v>
+        <v>549</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>654</v>
+        <v>472</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="9" t="s">
-        <v>174</v>
+        <v>142</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="141.75" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>181</v>
+        <v>550</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>655</v>
+        <v>473</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="9" t="s">
-        <v>184</v>
+        <v>142</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="141.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>185</v>
+        <v>551</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>656</v>
+        <v>474</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="9" t="s">
-        <v>188</v>
+        <v>142</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="141.75" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>189</v>
+        <v>552</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>657</v>
+        <v>475</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="9" t="s">
-        <v>192</v>
+        <v>142</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="141.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>193</v>
+        <v>553</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>658</v>
+        <v>476</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="9" t="s">
-        <v>196</v>
+        <v>142</v>
+      </c>
+      <c r="F17" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="141.75" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>197</v>
+        <v>554</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>659</v>
+        <v>477</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="9" t="s">
-        <v>200</v>
+        <v>142</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="141.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>201</v>
+        <v>555</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>660</v>
+        <v>478</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="9" t="s">
-        <v>204</v>
+        <v>142</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>205</v>
+        <v>556</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>661</v>
+        <v>479</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="9" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>209</v>
+        <v>557</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>662</v>
+        <v>480</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="9" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>212</v>
+        <v>558</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>663</v>
+        <v>481</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="9" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>215</v>
+        <v>559</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>664</v>
+        <v>482</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="9" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>218</v>
+        <v>560</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>665</v>
+        <v>483</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>649</v>
+        <v>467</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="9" t="s">
-        <v>220</v>
+        <v>142</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>221</v>
+        <v>561</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>666</v>
+        <v>484</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="9" t="s">
-        <v>220</v>
+        <v>142</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="139.5" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>224</v>
+        <v>562</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>667</v>
+        <v>485</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="9" t="s">
-        <v>220</v>
+        <v>142</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="139.5" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>227</v>
+        <v>563</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>668</v>
+        <v>486</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="9" t="s">
-        <v>230</v>
+        <v>142</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>231</v>
+        <v>564</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>669</v>
+        <v>487</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="9" t="s">
-        <v>234</v>
+        <v>142</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>235</v>
+        <v>565</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>670</v>
+        <v>488</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="9" t="s">
-        <v>238</v>
+        <v>142</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>239</v>
+        <v>566</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>671</v>
+        <v>489</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="9" t="s">
-        <v>242</v>
+        <v>142</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="139.5" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>243</v>
+        <v>567</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C31" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H31" s="34" t="s">
         <v>675</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="9" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="139.5" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>246</v>
+        <v>568</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>247</v>
+        <v>186</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>672</v>
+        <v>490</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="9" t="s">
-        <v>249</v>
+        <v>142</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="141.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>250</v>
+        <v>569</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>251</v>
+        <v>188</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>673</v>
+        <v>491</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="9" t="s">
-        <v>249</v>
+        <v>142</v>
+      </c>
+      <c r="F33" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="35">
+        <v>46318</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -8779,8 +9034,8 @@
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="25" style="36" customWidth="1"/>
-    <col min="2" max="2" width="36" style="36" customWidth="1"/>
+    <col min="1" max="1" width="25" style="21" customWidth="1"/>
+    <col min="2" max="2" width="36" style="21" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
     <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
@@ -8791,8 +9046,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="38"/>
-      <c r="B1" s="30"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="15"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -8801,75 +9056,75 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+    </row>
+    <row r="5" spans="1:8" ht="24" customHeight="1">
+      <c r="A5" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="39" t="s">
+      <c r="B5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="39" t="s">
+      <c r="C5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="D5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="F5" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
-      <c r="A6" s="41">
+      <c r="A6" s="25">
         <f>COUNTIF($F$9:$F$33,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="17">
         <f>COUNTIF($F$9:$F$33,"Failed")</f>
         <v>0</v>
       </c>
@@ -8885,16 +9140,16 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="59">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="45"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -8903,629 +9158,629 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="E8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>254</v>
+      <c r="A9" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>190</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A10" s="44" t="s">
-        <v>258</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>259</v>
+      <c r="A10" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>194</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="9" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>60</v>
+      <c r="A11" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="9" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A12" s="44" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>61</v>
+      <c r="A12" s="28" t="s">
+        <v>573</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="9" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>270</v>
+      <c r="A13" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>202</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="9" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A14" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>274</v>
+      <c r="A14" s="28" t="s">
+        <v>575</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>205</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="9" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A15" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>279</v>
+      <c r="A15" s="27" t="s">
+        <v>576</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>209</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="9" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A16" s="44" t="s">
-        <v>283</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>284</v>
+      <c r="A16" s="28" t="s">
+        <v>577</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>213</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>286</v>
+        <v>215</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="9" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A17" s="43" t="s">
-        <v>288</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>289</v>
+      <c r="A17" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>217</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="9" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A18" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>294</v>
+      <c r="A18" s="28" t="s">
+        <v>579</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>221</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="9" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A19" s="43" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>297</v>
+      <c r="A19" s="27" t="s">
+        <v>580</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>223</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="9" t="s">
-        <v>300</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A20" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>302</v>
+      <c r="A20" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>227</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>303</v>
+        <v>228</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="9" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A21" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>306</v>
+      <c r="A21" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="9" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A22" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>311</v>
+      <c r="A22" s="28" t="s">
+        <v>583</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>234</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>313</v>
+        <v>236</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="9" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A23" s="43" t="s">
-        <v>314</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>315</v>
+      <c r="A23" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>237</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>316</v>
+        <v>238</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>317</v>
+        <v>239</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="9" t="s">
-        <v>318</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A24" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>320</v>
+      <c r="A24" s="28" t="s">
+        <v>585</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>241</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>321</v>
+        <v>242</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="9" t="s">
-        <v>323</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A25" s="43" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>325</v>
+      <c r="A25" s="27" t="s">
+        <v>586</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>245</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>326</v>
+        <v>246</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>327</v>
+        <v>247</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="9" t="s">
-        <v>328</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A26" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>330</v>
+      <c r="A26" s="28" t="s">
+        <v>587</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>249</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>331</v>
+        <v>250</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="9" t="s">
-        <v>333</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A27" s="43" t="s">
-        <v>334</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>335</v>
+      <c r="A27" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>253</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>336</v>
+        <v>254</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="9" t="s">
-        <v>333</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A28" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>339</v>
+      <c r="A28" s="28" t="s">
+        <v>589</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>256</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>341</v>
+        <v>258</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="9" t="s">
-        <v>333</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A29" s="43" t="s">
-        <v>342</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>343</v>
+      <c r="A29" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>259</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>345</v>
+        <v>261</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="9" t="s">
-        <v>346</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A30" s="44" t="s">
-        <v>347</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>348</v>
+      <c r="A30" s="28" t="s">
+        <v>591</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>263</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="9" t="s">
-        <v>351</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="156" customHeight="1">
-      <c r="A31" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>353</v>
+      <c r="A31" s="27" t="s">
+        <v>592</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>354</v>
+        <v>268</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="9" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="156" customHeight="1">
-      <c r="A32" s="44" t="s">
-        <v>357</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>358</v>
+      <c r="A32" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>271</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>359</v>
+        <v>272</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>360</v>
+        <v>273</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="9" t="s">
-        <v>361</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A33" s="43" t="s">
-        <v>362</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>363</v>
+      <c r="A33" s="27" t="s">
+        <v>594</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="9" t="s">
-        <v>356</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -10557,67 +10812,67 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+        <v>42</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="F5" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
@@ -10640,12 +10895,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="59">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -10659,628 +10914,628 @@
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>366</v>
+        <v>595</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>368</v>
+        <v>279</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="9" t="s">
-        <v>371</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="139.5" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>372</v>
+        <v>596</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>373</v>
+        <v>283</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>374</v>
+        <v>284</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>375</v>
+        <v>285</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="9" t="s">
-        <v>376</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="139.5" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>377</v>
+        <v>597</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>379</v>
+        <v>288</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>380</v>
+        <v>289</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="9" t="s">
-        <v>376</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="139.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>381</v>
+        <v>598</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>382</v>
+        <v>290</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>384</v>
+        <v>292</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="9" t="s">
-        <v>376</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="139.5" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>385</v>
+        <v>599</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>386</v>
+        <v>293</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>387</v>
+        <v>294</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>388</v>
+        <v>295</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="9" t="s">
-        <v>376</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="139.5" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>389</v>
+        <v>600</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>390</v>
+        <v>296</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>391</v>
+        <v>297</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>392</v>
+        <v>298</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="9" t="s">
-        <v>393</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="139.5" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>394</v>
+        <v>601</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>396</v>
+        <v>301</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>397</v>
+        <v>302</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="9" t="s">
-        <v>398</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="139.5" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>399</v>
+        <v>602</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>401</v>
+        <v>305</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>402</v>
+        <v>306</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="9" t="s">
-        <v>398</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="139.5" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>403</v>
+        <v>603</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>405</v>
+        <v>308</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>406</v>
+        <v>309</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="9" t="s">
-        <v>398</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="139.5" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>407</v>
+        <v>604</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>408</v>
+        <v>310</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>409</v>
+        <v>311</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>410</v>
+        <v>312</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="9" t="s">
-        <v>411</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="139.5" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>412</v>
+        <v>605</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>413</v>
+        <v>314</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>414</v>
+        <v>315</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>415</v>
+        <v>316</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="9" t="s">
-        <v>416</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>417</v>
+        <v>606</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>419</v>
+        <v>319</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="9" t="s">
-        <v>421</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>422</v>
+        <v>607</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>425</v>
+        <v>324</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="9" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>427</v>
+        <v>608</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>428</v>
+        <v>326</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>429</v>
+        <v>327</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>430</v>
+        <v>328</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="9" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>432</v>
+        <v>609</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>433</v>
+        <v>330</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>435</v>
+        <v>332</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="9" t="s">
-        <v>436</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>437</v>
+        <v>610</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>439</v>
+        <v>335</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>440</v>
+        <v>336</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="9" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>442</v>
+        <v>611</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>443</v>
+        <v>338</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>444</v>
+        <v>339</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>445</v>
+        <v>340</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="9" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="141.75" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>446</v>
+        <v>612</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>448</v>
+        <v>342</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>449</v>
+        <v>343</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="9" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="141.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>450</v>
+        <v>613</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>451</v>
+        <v>344</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>452</v>
+        <v>345</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="9" t="s">
-        <v>454</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>455</v>
+        <v>614</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>456</v>
+        <v>348</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>457</v>
+        <v>349</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>458</v>
+        <v>350</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="9" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>459</v>
+        <v>615</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>460</v>
+        <v>351</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>461</v>
+        <v>352</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>462</v>
+        <v>353</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="9" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>464</v>
+        <v>616</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>465</v>
+        <v>355</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>466</v>
+        <v>356</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>467</v>
+        <v>357</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="9" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="139.5" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>469</v>
+        <v>358</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>470</v>
+        <v>359</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>471</v>
+        <v>360</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="9" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="139.5" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>472</v>
+        <v>618</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>473</v>
+        <v>361</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>474</v>
+        <v>362</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>475</v>
+        <v>363</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="9" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="139.5" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>476</v>
+        <v>619</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>477</v>
+        <v>364</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>478</v>
+        <v>365</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>479</v>
+        <v>366</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="9" t="s">
-        <v>463</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -12283,7 +12538,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F996"/>
+  <dimension ref="A1:F965"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -12304,14 +12559,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>480</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="A2" s="53" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -12323,362 +12578,362 @@
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="99.6" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="109.5" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>674</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>483</v>
+        <v>369</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="109.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>485</v>
+        <v>370</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>486</v>
+        <v>371</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>487</v>
+        <v>372</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>488</v>
+        <v>373</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>489</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="109.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>490</v>
+        <v>375</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>491</v>
+        <v>376</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>492</v>
+        <v>377</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>493</v>
+        <v>378</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>494</v>
+        <v>379</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>495</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="109.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>496</v>
+        <v>381</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>497</v>
+        <v>382</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>498</v>
+        <v>383</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>499</v>
+        <v>621</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>500</v>
+        <v>384</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>501</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="109.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>502</v>
+        <v>386</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>503</v>
+        <v>387</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>505</v>
+        <v>622</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>506</v>
+        <v>389</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>507</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="109.5" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>508</v>
+        <v>391</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>509</v>
+        <v>392</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>510</v>
+        <v>393</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>511</v>
+        <v>623</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>506</v>
+        <v>389</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>512</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="109.5" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>513</v>
+        <v>395</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>514</v>
+        <v>396</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>515</v>
+        <v>397</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>516</v>
+        <v>624</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>517</v>
+        <v>398</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>518</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="109.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>519</v>
+        <v>400</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>520</v>
+        <v>401</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>521</v>
+        <v>402</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>522</v>
+        <v>625</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>523</v>
+        <v>403</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="109.5" customHeight="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="114.6" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>525</v>
+        <v>405</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>526</v>
+        <v>406</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>527</v>
+        <v>407</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>528</v>
+        <v>626</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>529</v>
+        <v>408</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>530</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="109.5" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>531</v>
+        <v>410</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>532</v>
+        <v>411</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>533</v>
+        <v>412</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>535</v>
+        <v>413</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>536</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="109.5" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>537</v>
+        <v>415</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>538</v>
+        <v>416</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>539</v>
+        <v>417</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>540</v>
+        <v>628</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>541</v>
+        <v>418</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>542</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="109.5" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>543</v>
+        <v>420</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>544</v>
+        <v>421</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>545</v>
+        <v>422</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>546</v>
+        <v>619</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>547</v>
+        <v>423</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>548</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="109.5" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>549</v>
+        <v>425</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>550</v>
+        <v>426</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>551</v>
+        <v>427</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>552</v>
+        <v>629</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>553</v>
+        <v>428</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="109.5" customHeight="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="115.2" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>555</v>
+        <v>430</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>557</v>
+        <v>431</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>558</v>
+        <v>630</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>559</v>
+        <v>432</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>560</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="109.5" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>561</v>
+        <v>434</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>562</v>
+        <v>435</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>563</v>
+        <v>436</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>558</v>
+        <v>630</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>564</v>
+        <v>437</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>565</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="109.5" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>566</v>
+        <v>439</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>567</v>
+        <v>440</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>568</v>
+        <v>441</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>569</v>
+        <v>631</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>570</v>
+        <v>442</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>571</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="109.5" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>572</v>
+        <v>444</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>573</v>
+        <v>445</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>574</v>
+        <v>446</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>575</v>
+        <v>447</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>577</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
@@ -12691,13 +12946,13 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -12705,13 +12960,13 @@
     </row>
     <row r="24" spans="1:6" ht="69.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="B24" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="B24" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="29" t="s">
-        <v>642</v>
+      <c r="C24" s="14" t="s">
+        <v>460</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -12719,13 +12974,13 @@
     </row>
     <row r="25" spans="1:6" ht="69.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>580</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>643</v>
+        <v>451</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>452</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>461</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -12733,13 +12988,13 @@
     </row>
     <row r="26" spans="1:6" ht="69.75" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>582</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>644</v>
+        <v>453</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>462</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -12747,13 +13002,13 @@
     </row>
     <row r="27" spans="1:6" ht="69.75" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>584</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>645</v>
+        <v>455</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>463</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -12761,27 +13016,27 @@
     </row>
     <row r="28" spans="1:6" ht="69.75" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>586</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>646</v>
+        <v>457</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>464</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" ht="69.75" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>647</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>587</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>648</v>
+      <c r="A29" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>466</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -12795,66 +13050,24 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -13772,37 +13985,6 @@
     <row r="963" ht="15.75" customHeight="1"/>
     <row r="964" ht="15.75" customHeight="1"/>
     <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -13842,14 +14024,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="A2" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -13864,279 +14046,279 @@
         <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="103.5" customHeight="1">
+    </row>
+    <row r="5" spans="1:6" ht="150" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>628</v>
+        <v>497</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>498</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>589</v>
+        <v>499</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="103.5" customHeight="1">
+        <v>500</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="150" customHeight="1">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>592</v>
+        <v>501</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>629</v>
+        <v>502</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>593</v>
+        <v>503</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="103.5" customHeight="1">
+        <v>504</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="150" customHeight="1">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>595</v>
+        <v>505</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>630</v>
+        <v>506</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>596</v>
+        <v>507</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="103.5" customHeight="1">
+        <v>508</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="150" customHeight="1">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>598</v>
+        <v>509</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>631</v>
+        <v>510</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>599</v>
+        <v>511</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="103.5" customHeight="1">
+        <v>512</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="150" customHeight="1">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>601</v>
+        <v>513</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>632</v>
+        <v>514</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>602</v>
+        <v>515</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="103.5" customHeight="1">
+        <v>516</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="150" customHeight="1">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>604</v>
+        <v>517</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>605</v>
+        <v>518</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="103.5" customHeight="1">
+        <v>519</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="150" customHeight="1">
       <c r="A11" s="4">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>607</v>
+        <v>520</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>608</v>
+        <v>521</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="103.5" customHeight="1">
+        <v>522</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="150" customHeight="1">
       <c r="A12" s="4">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>610</v>
+        <v>523</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>611</v>
+        <v>524</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="103.5" customHeight="1">
+        <v>525</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="150" customHeight="1">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>613</v>
+        <v>526</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>614</v>
+        <v>527</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="103.2" customHeight="1">
+        <v>528</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="150" customHeight="1">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>616</v>
+        <v>529</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>637</v>
+        <v>530</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>617</v>
+        <v>531</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="102" customHeight="1">
+        <v>532</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="150" customHeight="1">
       <c r="A15" s="4">
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>619</v>
+        <v>533</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>638</v>
+        <v>534</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>620</v>
+        <v>535</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="102.6" customHeight="1">
+        <v>536</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="150" customHeight="1">
       <c r="A16" s="4">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>622</v>
+        <v>537</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>639</v>
+        <v>538</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="102.6" customHeight="1">
+        <v>540</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="150" customHeight="1">
       <c r="A17" s="4">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>625</v>
+        <v>541</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>640</v>
+        <v>542</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>626</v>
+        <v>543</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>591</v>
+        <v>544</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15172,16 +15354,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="42" customHeight="1">
-      <c r="B1" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="1"/>
@@ -15194,58 +15376,58 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="14" t="str">
+      <c r="C3" s="54"/>
+      <c r="D3" s="46" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14" t="str">
+      <c r="C4" s="54"/>
+      <c r="D4" s="46" t="str">
         <f>Cover!C6</f>
         <v>Group01_23130299_NguyenVanThang</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="B5" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="B6" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="1"/>
@@ -15272,25 +15454,25 @@
         <v>28</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="I9" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="30" customHeight="1">
@@ -15298,19 +15480,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D10" s="4">
         <f>RECRUIT_VAC!A6</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E10" s="4">
         <f>RECRUIT_VAC!B6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="4">
         <f>RECRUIT_VAC!C6</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4">
         <f>RECRUIT_VAC!D6</f>
@@ -15330,7 +15512,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="D11" s="4">
         <f>RECRUIT_CAND!A6</f>
@@ -15362,7 +15544,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="D12" s="4">
         <f>RECRUIT_FLOW!A6</f>
@@ -15400,21 +15582,21 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="18"/>
+      <c r="B14" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="47"/>
       <c r="D14" s="13">
         <f t="shared" ref="D14:I14" si="0">SUM(D10:D12)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="0"/>
@@ -15450,31 +15632,31 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="27">
+      <c r="B17" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="62">
         <f>IF(I14=0,"",(D14+E14)/I14)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F17" s="54"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="27" t="str">
+      <c r="B18" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="62">
         <f>IF(D14+E14=0,"Chưa thực thi",D14/(D14+E14))</f>
-        <v>Chưa thực thi</v>
-      </c>
-      <c r="F18" s="15"/>
+        <v>0.92</v>
+      </c>
+      <c r="F18" s="54"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -15490,16 +15672,16 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B20" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
+      <c r="B20" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
     </row>
     <row r="21" spans="2:9" ht="15.75" customHeight="1">
       <c r="B21" s="1"/>
@@ -15512,16 +15694,16 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B22" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+      <c r="B22" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" spans="2:9" ht="15.75" customHeight="1">
       <c r="B23" s="1"/>

--- a/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
+++ b/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\IdeaProjects\OrangeHRM-Testing\docs\test-cases\members\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC5761-3207-479C-8090-CBC40704B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06DDC80-8750-4450-BA57-36138A8AB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="694">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -2615,6 +2615,12 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>RECRUIT_VAC_20261023_01</t>
+  </si>
+  <si>
+    <t>Katalon Studio / Chrome 155.0.8059.85</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +2826,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2931,6 +2937,27 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2949,14 +2976,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2969,13 +2988,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2991,13 +3006,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3363,14 +3372,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
@@ -3386,11 +3395,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="3" t="s">
         <v>2</v>
       </c>
@@ -3403,11 +3412,11 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
@@ -3417,14 +3426,14 @@
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
@@ -3434,10 +3443,10 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3560,78 +3569,78 @@
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="54">
         <v>23130299</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" ht="24.75" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" ht="24.75" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="2:8" ht="24.75" customHeight="1">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="2:8" ht="36" customHeight="1">
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="2:8" ht="24.75" customHeight="1">
       <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="52"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" customHeight="1">
@@ -4656,13 +4665,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
@@ -4676,43 +4685,43 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="46" t="str">
+      <c r="C4" s="41"/>
+      <c r="D4" s="40" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="46" t="str">
+      <c r="C5" s="41"/>
+      <c r="D5" s="40" t="str">
         <f>Cover!C5</f>
         <v>Group01_OrangeHRM</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8" ht="48" customHeight="1">
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="41" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="50" t="s">
         <v>652</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="60"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
@@ -4820,11 +4829,11 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="37.5" customHeight="1">
-      <c r="B14" s="52"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
@@ -4838,11 +4847,11 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B16" s="52"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
@@ -7254,43 +7263,43 @@
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
@@ -7308,11 +7317,11 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
@@ -7335,12 +7344,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="62">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -9059,43 +9068,43 @@
       <c r="A2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="24" t="s">
@@ -9113,11 +9122,11 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="25">
@@ -9140,12 +9149,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="62">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="29"/>
@@ -10814,43 +10823,43 @@
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
@@ -10868,11 +10877,11 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
@@ -10895,12 +10904,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="62">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -12559,14 +12568,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="57" t="s">
         <v>367</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -14024,14 +14033,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -15354,16 +15363,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="42" customHeight="1">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="1"/>
@@ -15376,58 +15385,64 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="46" t="str">
+      <c r="C3" s="41"/>
+      <c r="D3" s="40" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="46" t="str">
+      <c r="C4" s="41"/>
+      <c r="D4" s="40" t="str">
         <f>Cover!C6</f>
         <v>Group01_23130299_NguyenVanThang</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42" t="s">
+        <v>692</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="63">
+        <v>46318.496458333335</v>
+      </c>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42" t="s">
+        <v>693</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="1"/>
@@ -15582,10 +15597,10 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="43"/>
       <c r="D14" s="13">
         <f t="shared" ref="D14:I14" si="0">SUM(D10:D12)</f>
         <v>23</v>
@@ -15632,31 +15647,31 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="62">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="46">
         <f>IF(I14=0,"",(D14+E14)/I14)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F17" s="54"/>
+      <c r="F17" s="41"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="62">
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="46">
         <f>IF(D14+E14=0,"Chưa thực thi",D14/(D14+E14))</f>
         <v>0.92</v>
       </c>
-      <c r="F18" s="54"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -15672,16 +15687,16 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
     </row>
     <row r="21" spans="2:9" ht="15.75" customHeight="1">
       <c r="B21" s="1"/>
@@ -15694,16 +15709,16 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
     </row>
     <row r="23" spans="2:9" ht="15.75" customHeight="1">
       <c r="B23" s="1"/>
@@ -16694,11 +16709,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="D6:I6"/>
@@ -16711,6 +16721,11 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
+++ b/docs/test-cases/members/Group01_23130299_NguyenVanThang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\IdeaProjects\OrangeHRM-Testing\docs\test-cases\members\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06DDC80-8750-4450-BA57-36138A8AB5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6AB4FE-39FC-4F52-BFD0-0D3C57F71ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="698">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -614,14 +614,6 @@
   </si>
   <si>
     <t>Tạo ứng viên tối thiểu</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: First=An; Last=NguyenRUN01; Email=an.run01@example.com; Vacancy=VAC_A
-1. Vào Recruitment &gt; Candidates &gt; Add.
-2. Nhập First, Last, Email và chọn VAC_A.
-3. Save; trở lại list, tìm đúng email và mở hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
   </si>
   <si>
     <t>Tạo được ứng viên; tên, email và vacancy đúng input.</t>
@@ -633,14 +625,6 @@
   </si>
   <si>
     <t>Tạo ứng viên với thông tin đầy đủ</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: First=Minh; Middle=Quang; Last=TranRUN02; Email=minh.run02@example.com; Phone=0900000002; Keywords=java,qa; Notes=demo; VAC_A
-1. Mở Add Candidate; nhập đủ dữ liệu và chọn VAC_A.
-2. Chọn consent theo trạng thái cho phép lưu; Save.
-3. Mở hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
   </si>
   <si>
     <t>Lưu đúng tên đầy đủ, email, phone, vacancy, keyword và notes.</t>
@@ -687,53 +671,10 @@
     <t>Không chọn Vacancy tùy chọn</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: First=An; Last=NguyenRUN06; Email=run06@example.com; Vacancy rỗng
-1. Mở Add Candidate, điền First/Last/Email.
-2. Để trống Vacancy; Save; mở hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Nếu demo cho phép vacancy tùy chọn: lưu ứng viên và hiển thị Vacancy rỗng; ghi nhận chính xác hành vi.</t>
-  </si>
-  <si>
-    <t>TD_RECRUIT_CAND_01
-Positive; Phân vùng tương đương
-Automation: P1
-Cần kiểm tra UI: Theo hướng dẫn OrangeHRM, Vacancy không đánh dấu bắt buộc; kiểm tra trên demo.</t>
-  </si>
-  <si>
     <t>Kiểm tra consent khi tạo hồ sơ</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: First=An; Last=NguyenRUN07; Email=run07@example.com; Consent=On
-1. Mở Add Candidate, nhập thông tin bắt buộc.
-2. Bật checkbox consent (nếu có).
-3. Save và mở lại hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Lưu thành công; trạng thái consent đúng tùy chọn hoặc hệ thống có ghi nhận chọn đồng ý.</t>
-  </si>
-  <si>
-    <t>TD_RECRUIT_CAND_01
-Positive; Phân vùng tương đương
-Automation: P1
-Cần kiểm tra UI: Demo có thể chỉ hiển thị consent ở form riêng; điều chỉnh nếu UI khác.</t>
-  </si>
-  <si>
     <t>Email hợp lệ dạng example.com</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: Email=quality.run08@example.com
-1. Add ứng viên tên riêng hợp lệ với email hợp lệ.
-2. Save và mở lại.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Email được lưu nguyên vẹn; có thể tìm đúng hồ sơ.</t>
   </si>
   <si>
     <t>TD_RECRUIT_CAND_02
@@ -770,22 +711,6 @@
   </si>
   <si>
     <t>Số điện thoại dạng chữ</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: Phone='abcXYZ'; Email=run11@example.com
-1. Add hồ sơ với tên và email hợp lệ, Phone=abcXYZ.
-2. Save; kiểm tra trạng thái và hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Không nhận số điện thoại sai dạng nếu có validation; ghi lại thông báo đúng UI.</t>
-  </si>
-  <si>
-    <t>TD_RECRUIT_CAND_02
-Negative; Phân vùng tương đương
-Automation: P1
-Cần kiểm tra UI: Demo có thể cho phép Phone tự do; xác nhận quy tắc trước khi khóa kỳ vọng.</t>
   </si>
   <si>
     <t>Số điện thoại hợp lệ</t>
@@ -855,22 +780,6 @@
     <t>Tải CV vượt dung lượng tối đa</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: resume_oversize.pdf; dung lượng CV_LIMIT+1 byte
-1. Đọc giới hạn file được hiển thị trên UI.
-2. Add Candidate, chọn file PDF vượt đúng 1 byte; Save.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi vượt giới hạn; file quá lớn không được đính kèm.</t>
-  </si>
-  <si>
-    <t>TD_RECRUIT_CAND_03
-Negative; Phân tích giá trị biên
-Automation: P1
-Cần kiểm tra UI: CV_LIMIT lấy từ demo, không áp dụng mặc định 5MB của bản thương mại.</t>
-  </si>
-  <si>
     <t>Hủy chọn CV trước lưu</t>
   </si>
   <si>
@@ -975,13 +884,6 @@
     <t>Sửa Keywords và Notes hồ sơ</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: CAND_EDIT; Keywords=playwright,regression; Notes='Updated RUN'
-1. Mở chi tiết CAND_EDIT; ghi baseline.
-2. Edit, đổi Keywords/Notes; Save; reload.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
     <t>Keywords và Notes đúng giá trị mới; email và vacancy không đổi.</t>
   </si>
   <si>
@@ -991,17 +893,6 @@
   </si>
   <si>
     <t>Hủy chỉnh sửa hồ sơ ứng viên</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
-Input: CAND_EDIT; Email tạm=unsaved@example.com
-1. Mở CAND_EDIT; ghi email gốc.
-2. Vào Edit, đổi email; nhấn Cancel/Back.
-3. Reload hồ sơ.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
-    <t>Email vẫn đúng baseline; không lưu email tạm.</t>
   </si>
   <si>
     <t>TD_RECRUIT_CAND_05
@@ -1066,14 +957,6 @@
     <t>Reject ứng viên từ trạng thái ban đầu</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
-Input: F_NEW_03 Application Initiated; Notes='Reject initial RUN'
-1. Mở F_NEW_03.
-2. Nhấn Reject; xác nhận trong hộp thoại.
-3. Reload.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
     <t>Status chuyển Rejected; Candidate History có sự kiện reject.</t>
   </si>
   <si>
@@ -1091,17 +974,6 @@
     <t>Trạng thái Rejected; lịch sử còn sự kiện shortlist cũ và thêm reject.</t>
   </si>
   <si>
-    <t>Hủy hộp thoại Shortlist</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
-Input: F_NEW_05 Application Initiated; Notes='Không được lưu'
-1. Mở F_NEW_05; nhấn Shortlist.
-2. Điền Notes nếu có; nhấn Cancel/Back thay vì xác nhận.
-3. Reload.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
     <t>Status vẫn Application Initiated; History không có sự kiện Shortlist mới.</t>
   </si>
   <si>
@@ -1247,21 +1119,7 @@
     <t>Chọn nhiều interviewer</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
-Input: F_SHORT_14; INT_A và INT_B khác người
-1. Mở Schedule Interview.
-2. Chọn INT_A, tiếp tục chọn INT_B qua suggestion.
-3. Điền Title/Date; Save; mở lại.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
     <t>Lưu đúng cả hai interviewer, không trùng; hiển thị đúng trên chi tiết.</t>
-  </si>
-  <si>
-    <t>TD_RECRUIT_FLOW_03
-Positive; Phân vùng tương đương
-Automation: P1
-Cần kiểm tra UI: Chỉ chạy nếu bản demo hỗ trợ multi-select; nếu không, ghi Blocked và phiên bản.</t>
   </si>
   <si>
     <t>Không chọn interviewer đã xóa</t>
@@ -1341,34 +1199,13 @@
     <t>Không hiển thị thao tác Shortlist trái quy tắc trạng thái; status vẫn Rejected.</t>
   </si>
   <si>
-    <t>TD_RECRUIT_FLOW_04
-Positive; Chuyển trạng thái
-Automation: P1
-Cần kiểm tra UI: Ghi nhận flow nếu phiên bản hỗ trợ Re-activate ứng viên.</t>
-  </si>
-  <si>
     <t>Hủy Reject không đổi trạng thái</t>
   </si>
   <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
-Input: F_SHORT_20 Shortlisted
-1. Mở F_SHORT_20; nhấn Reject.
-2. Nhấn Cancel/Back trong dialog.
-3. Reload chi tiết.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
-  </si>
-  <si>
     <t>Vẫn Shortlisted; không thêm bản ghi Reject vào History.</t>
   </si>
   <si>
     <t>Candidate Details chứa đúng bản ghi</t>
-  </si>
-  <si>
-    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
-Input: F_NEW_21; name/email/vacancy cố định theo Test Data
-1. Vào Candidates; tìm bằng email F_NEW_21.
-2. Mở chi tiết, đối chiếu name/email/vacancy.
-Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
   </si>
   <si>
     <t>Tên, email, vacancy và trạng thái đúng một ứng viên; không hiển thị fixture khác.</t>
@@ -2621,6 +2458,186 @@
   </si>
   <si>
     <t>Katalon Studio / Chrome 155.0.8059.85</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: First=An; Last=NguyenRUN01; Email=an.run01@example.com; Vacancy=VAC_A
+1. Vào Recruitment &gt; Candidates &gt; Add.
+2. Nhập First, Last, Email và chọn VAC_A.
+3. Save và ghi lại Candidate ID; mở lại hồ sơ để xác minh dữ liệu đã lưu.
+4. Trở lại Candidates; tìm bằng Candidate Name, chọn đúng gợi ý, Search, mở đúng hồ sơ theo fixture/ID và đối chiếu Email với input (không tìm theo Email ở bộ lọc list).
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: First=Minh; Middle=Quang; Last=TranRUN02; Email=minh.run02@example.com; Phone=0900000002; Keywords=java,qa; Notes=demo; VAC_A
+1. Mở Add Candidate; nhập đủ dữ liệu và chọn VAC_A.
+2. Ghi nhận trạng thái checkbox Consent to keep data (không phải trường bắt buộc); Save.
+3. Mở hồ sơ.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: First=An; Last=NguyenRUN06; Email=run06@example.com; Vacancy rỗng
+1. Mở Add Candidate, điền First/Last/Email.
+2. Để trống Vacancy (không có rule Required trong Add Candidate); Save; mở lại hồ sơ nếu server chấp nhận.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Trường Vacancy không báo Required ở frontend; nếu server lưu thành công, hồ sơ mở lại có Vacancy trống. Ghi nhận riêng kết quả backend khi chạy thực tế.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_CAND_01
+Positive; Phân vùng tương đương
+Automation: P1
+Đối chiếu app.js: Add Candidate không gán Required cho Vacancy; xác minh lưu với vacancyId=null khi chạy trên demo.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: First=An; Last=NguyenRUN07; Email=run07@example.com; Consent=On
+1. Mở Add Candidate, nhập thông tin bắt buộc.
+2. Bật checkbox Consent to keep data (form Add Candidate thực sự có trường này).
+3. Save, mở lại Candidate Profile và đối chiếu trạng thái consent được lưu.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Candidate được lưu; Consent to keep data vẫn bật sau khi mở lại hồ sơ đúng Candidate ID.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_CAND_01
+Positive; Phân vùng tương đương
+Automation: P1
+Đã xác minh trong app.js: checkbox consentToKeepData xuất hiện cả ở Add Candidate và Profile.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: Email=quality.run08@example.com
+1. Add ứng viên tên riêng hợp lệ với email hợp lệ.
+2. Save; lấy Candidate ID, mở lại đúng Profile và xác minh Email bằng giá trị input.
+3. Nếu kiểm tra list, tìm bằng Candidate Name + xác minh ID; không dùng Email filter.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Email hợp lệ được lưu nguyên vẹn trong Candidate Profile sau khi mở lại đúng Candidate ID; không yêu cầu bộ lọc Email.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: Phone='abcXYZ'; Email=run11@example.com
+1. Add hồ sơ với tên và email hợp lệ, Phone=abcXYZ.
+2. Nhập Phone=abcXYZ, thử Save; xác minh lỗi validation tại Contact Number và không có hồ sơ mới.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Contact Number báo lỗi định dạng (chỉ chấp nhận chữ số và + - / ( ) dấu cách); Save không tạo Candidate khi nhập 'abcXYZ'.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_CAND_02
+Negative; Phân vùng tương đương
+Automation: P1
+Đối chiếu app.js: contactNumber validator /^[0-9+\-/() ]+$/; chữ abcXYZ bị từ chối trước khi Save; xác minh thông báo khi runtime.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: resume_oversize.pdf; dung lượng đúng maxFileSize+1 byte sau khi xác minh maxFileSize numeric trong cấu hình render Add Candidate.
+1. Xác minh giá trị maxFileSize (byte) từ cấu hình trang/component Add Candidate; đối chiếu nhãn dung lượng hiển thị, không suy ra chỉ từ '1 MB'. Nếu thiếu giá trị numeric thì ghi Needs verification, chưa chạy phép thử biên.
+2. Add Candidate, chọn PDF có kích thước maxFileSize+1 byte; thử Save và xác minh lỗi tại Resume; không phát sinh attachment quá cỡ.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>File Resume &gt; maxFileSize (byte) bị từ chối bằng validation của file-upload; không lưu attachment quá giới hạn. Phải xác minh maxFileSize thực tế trước khi chạy test biên.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_CAND_03
+Negative; Phân tích giá trị biên
+Automation: P1
+app.js: Resume có rules uo(maxFileSize), po(allowedFileTypes); formattedFileSize dùng /1048576 để hiển thị, KHÔNG đủ để suy ra exact numeric maxFileSize. Cần cấu hình thật của Add Candidate.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: CAND_EDIT; Keywords=playwright,regression; Notes='Updated RUN'
+1. Mở chi tiết CAND_EDIT; ghi baseline.
+2. Bật Edit trên Candidate Profile; đổi Keywords/Notes; Save; reload đúng Profile ID.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; có VAC_A đang hiệu lực; email example.com và fixture hồ sơ riêng theo RUN_ID.
+Input: CAND_EDIT; Email tạm=unsaved@example.com
+1. Mở CAND_EDIT; ghi email gốc.
+2. Bật Edit, đổi email tạm nhưng KHÔNG Save; rời Candidate Profile qua Recruitment &gt; Candidates.
+3. Mở lại chính Candidate ID và kiểm tra Email vẫn là baseline.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Email sau khi mở lại đúng Candidate ID vẫn là baseline; email chưa Save không được ghi vào hồ sơ.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
+Input: F_NEW_03 Application Initiated; Notes='Reject initial RUN'
+1. Mở F_NEW_03.
+2. Nhấn Reject để mở trang hành động; điền Notes nếu cần và Save.
+3. Reload.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Hủy thao tác Shortlist trước khi Save</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
+Input: F_NEW_05 Application Initiated; Notes='Không được lưu'
+1. Mở F_NEW_05; nhấn Shortlist để mở trang thao tác.
+2. Điền Notes nếu có; nhấn Cancel trên trang Shortlist trước khi Save.
+3. Reload.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
+Input: F_SHORT_14; INT_A và INT_B khác người
+1. Mở Schedule Interview.
+2. Chọn INT_A, bấm Add another (nếu control hiện), chọn INT_B từ đúng gợi ý, mỗi người chỉ xuất hiện một lần.
+3. Điền Title/Date; Save; mở lại.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_FLOW_03
+Positive; Phân vùng tương đương
+Automation: P1
+Đối chiếu app.js: giao diện ScheduleInterview có mảng interviewers và onAddInterviewer() tối đa 5 trường; vẫn cần xác minh 2 nhân viên hợp lệ lúc runtime.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_FLOW_04
+Positive; Chuyển trạng thái
+Automation: P1
+Cần xác minh runtime: frontend hiển thị nút theo GET /api/v2/recruitment/candidates/{id}/actions/allowed, không hardcode trạng thái.</t>
+  </si>
+  <si>
+    <t>TD_RECRUIT_FLOW_04
+Positive; Chuyển trạng thái
+Automation: P1
+Cần xác minh runtime: frontend hiển thị action theo API /actions/allowed; không thể suy luận trạng thái terminal chỉ từ bundle.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
+Input: F_SHORT_20 Shortlisted
+1. Mở F_SHORT_20; nhấn Reject.
+2. Trên trang Reject, nhấn Cancel trước Save (không giả định có dialog).
+3. Reload chi tiết.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện: Đã đăng nhập Admin/Recruitment; VAC_A và INTERVIEWER_A/B hiệu lực; ứng viên độc lập đúng trạng thái đầu vào.
+Input: F_NEW_21; name/email/vacancy cố định theo Test Data
+1. Vào Candidates; nhập Candidate Name của F_NEW_21, chọn đúng gợi ý và Search (không có Email filter).
+2. Mở đúng Candidate Profile (đối chiếu Candidate ID từ fixture), kiểm tra tên, Email, Vacancy và Status.
+Kết thúc: khôi phục / dọn dẹp fixture theo Test Data; không dùng bản ghi của người khác.</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>RECRUIT_CAND RECRUIT_FLOW Automation</t>
+  </si>
+  <si>
+    <t>Triển khai 50 test case bằng Katalon Studio 11.6; kết quả 1 Pass, 24 Fail, 25 Skipped; bổ sung Test Report và Screenshot Evidence</t>
   </si>
 </sst>
 </file>
@@ -2826,7 +2843,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2853,12 +2870,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2934,29 +2945,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2973,7 +2974,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2988,11 +2993,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3000,14 +3005,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3372,14 +3392,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
@@ -3395,11 +3415,11 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="3" t="s">
         <v>2</v>
       </c>
@@ -3412,41 +3432,41 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="31">
         <v>46313</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3531,29 +3551,41 @@
         <v>46318</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="2:8" ht="45.75" customHeight="1">
-      <c r="B14" s="37"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+    <row r="14" spans="2:8" ht="73.2" customHeight="1">
+      <c r="B14" s="5">
+        <v>46325</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8">
@@ -3569,78 +3601,78 @@
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="50">
         <v>23130299</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:8" ht="24.75" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" ht="24.75" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="2:8" ht="24.75" customHeight="1">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="2:8" ht="36" customHeight="1">
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="47" t="s">
-        <v>651</v>
-      </c>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="41" t="s">
+        <v>624</v>
+      </c>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="2:8" ht="24.75" customHeight="1">
       <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" customHeight="1">
@@ -4665,13 +4697,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="42" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
@@ -4685,43 +4717,43 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="40" t="str">
+      <c r="C4" s="36"/>
+      <c r="D4" s="48" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="40" t="str">
+      <c r="C5" s="36"/>
+      <c r="D5" s="48" t="str">
         <f>Cover!C5</f>
         <v>Group01_OrangeHRM</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8" ht="48" customHeight="1">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="50" t="s">
-        <v>652</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="60"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="44" t="s">
+        <v>625</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="56"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
@@ -4795,7 +4827,7 @@
       <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -4829,11 +4861,11 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="37.5" customHeight="1">
-      <c r="B14" s="44"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
@@ -4847,11 +4879,11 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B16" s="44"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
@@ -5906,7 +5938,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="73.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5922,7 +5954,7 @@
         <v>103</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -5944,7 +5976,7 @@
         <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>637</v>
+        <v>610</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -5966,7 +5998,7 @@
         <v>108</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -5988,7 +6020,7 @@
         <v>111</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>639</v>
+        <v>612</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -6010,13 +6042,13 @@
         <v>108</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="78" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -6032,7 +6064,7 @@
         <v>39</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -6054,7 +6086,7 @@
         <v>39</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -6076,7 +6108,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -6098,7 +6130,7 @@
         <v>111</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>644</v>
+        <v>617</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -6120,13 +6152,13 @@
         <v>108</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>645</v>
+        <v>618</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="73.5" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>126</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -6142,7 +6174,7 @@
         <v>108</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>646</v>
+        <v>619</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -6164,7 +6196,7 @@
         <v>131</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -6186,7 +6218,7 @@
         <v>134</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -6208,7 +6240,7 @@
         <v>108</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -6230,7 +6262,7 @@
         <v>108</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>650</v>
+        <v>623</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -7263,43 +7295,43 @@
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
@@ -7317,11 +7349,11 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
@@ -7344,12 +7376,12 @@
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="40">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -7389,13 +7421,13 @@
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>468</v>
+      <c r="C9" s="29" t="s">
+        <v>441</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>141</v>
@@ -7403,51 +7435,51 @@
       <c r="E9" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="33">
         <v>46318</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>653</v>
+      <c r="H9" s="32" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>469</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="33">
         <v>46318</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>654</v>
+      <c r="H10" s="32" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="139.5" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>145</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>146</v>
@@ -7455,51 +7487,51 @@
       <c r="E11" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="33">
         <v>46318</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>655</v>
+      <c r="H11" s="32" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="33">
         <v>46318</v>
       </c>
-      <c r="H12" s="34" t="s">
-        <v>656</v>
+      <c r="H12" s="32" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="139.5" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>149</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>150</v>
@@ -7507,51 +7539,51 @@
       <c r="E13" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="33">
         <v>46318</v>
       </c>
-      <c r="H13" s="34" t="s">
-        <v>657</v>
+      <c r="H13" s="32" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="141.75" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="33">
         <v>46318</v>
       </c>
-      <c r="H14" s="34" t="s">
-        <v>658</v>
+      <c r="H14" s="32" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="141.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>153</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>154</v>
@@ -7559,51 +7591,51 @@
       <c r="E15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="33">
         <v>46318</v>
       </c>
-      <c r="H15" s="34" t="s">
-        <v>659</v>
+      <c r="H15" s="32" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="141.75" customHeight="1">
-      <c r="A16" s="12" t="s">
-        <v>552</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="33">
         <v>46318</v>
       </c>
-      <c r="H16" s="34" t="s">
-        <v>660</v>
+      <c r="H16" s="32" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="141.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>158</v>
@@ -7611,51 +7643,51 @@
       <c r="E17" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="33">
         <v>46318</v>
       </c>
-      <c r="H17" s="34" t="s">
-        <v>661</v>
+      <c r="H17" s="32" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="141.75" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="33">
         <v>46318</v>
       </c>
-      <c r="H18" s="34" t="s">
-        <v>662</v>
+      <c r="H18" s="32" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="141.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>162</v>
@@ -7663,51 +7695,51 @@
       <c r="E19" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="33">
         <v>46318</v>
       </c>
-      <c r="H19" s="34" t="s">
-        <v>663</v>
+      <c r="H19" s="32" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="D20" s="12" t="s">
+      <c r="C20" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="33">
         <v>46318</v>
       </c>
-      <c r="H20" s="34" t="s">
-        <v>664</v>
+      <c r="H20" s="32" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>166</v>
@@ -7715,51 +7747,51 @@
       <c r="E21" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="33">
         <v>46318</v>
       </c>
-      <c r="H21" s="34" t="s">
-        <v>665</v>
+      <c r="H21" s="32" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="33">
         <v>46318</v>
       </c>
-      <c r="H22" s="34" t="s">
-        <v>666</v>
+      <c r="H22" s="32" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>169</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>170</v>
@@ -7767,51 +7799,51 @@
       <c r="E23" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="33">
         <v>46318</v>
       </c>
-      <c r="H23" s="34" t="s">
-        <v>667</v>
+      <c r="H23" s="32" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A24" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="B24" s="12" t="s">
+      <c r="A24" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="33">
         <v>46318</v>
       </c>
-      <c r="H24" s="34" t="s">
-        <v>668</v>
+      <c r="H24" s="32" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>173</v>
@@ -7819,51 +7851,51 @@
       <c r="E25" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="33">
         <v>46318</v>
       </c>
-      <c r="H25" s="34" t="s">
-        <v>669</v>
+      <c r="H25" s="32" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="C26" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="33">
         <v>46318</v>
       </c>
-      <c r="H26" s="34" t="s">
-        <v>670</v>
+      <c r="H26" s="32" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="139.5" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>176</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>177</v>
@@ -7871,51 +7903,51 @@
       <c r="E27" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="33">
         <v>46318</v>
       </c>
-      <c r="H27" s="34" t="s">
-        <v>671</v>
+      <c r="H27" s="32" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A28" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="B28" s="12" t="s">
+      <c r="A28" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="C28" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="33">
         <v>46318</v>
       </c>
-      <c r="H28" s="34" t="s">
-        <v>672</v>
+      <c r="H28" s="32" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>565</v>
+        <v>538</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>180</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>181</v>
@@ -7923,51 +7955,51 @@
       <c r="E29" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="33">
         <v>46318</v>
       </c>
-      <c r="H29" s="34" t="s">
-        <v>673</v>
+      <c r="H29" s="32" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A30" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="B30" s="12" t="s">
+      <c r="A30" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="C30" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="36" t="s">
+      <c r="F30" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="33">
         <v>46318</v>
       </c>
-      <c r="H30" s="34" t="s">
-        <v>674</v>
+      <c r="H30" s="32" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="139.5" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C31" s="31" t="s">
-        <v>493</v>
+      <c r="C31" s="29" t="s">
+        <v>466</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>185</v>
@@ -7975,51 +8007,51 @@
       <c r="E31" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="33">
         <v>46318</v>
       </c>
-      <c r="H31" s="34" t="s">
-        <v>675</v>
+      <c r="H31" s="32" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A32" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="B32" s="12" t="s">
+      <c r="A32" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="36" t="s">
+      <c r="F32" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="33">
         <v>46318</v>
       </c>
-      <c r="H32" s="34" t="s">
-        <v>676</v>
+      <c r="H32" s="32" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="141.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>569</v>
+        <v>542</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>188</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>189</v>
@@ -8027,14 +8059,14 @@
       <c r="E33" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="33">
         <v>46318</v>
       </c>
-      <c r="H33" s="34" t="s">
-        <v>677</v>
+      <c r="H33" s="32" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -9043,8 +9075,8 @@
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="25" style="21" customWidth="1"/>
-    <col min="2" max="2" width="36" style="21" customWidth="1"/>
+    <col min="1" max="1" width="25" style="19" customWidth="1"/>
+    <col min="2" max="2" width="36" style="19" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
     <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
@@ -9055,8 +9087,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22"/>
-      <c r="B1" s="15"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="13"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -9065,52 +9097,52 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -9122,24 +9154,24 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <f>COUNTIF($F$9:$F$33,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <f>COUNTIF($F$9:$F$33,"Failed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="8">
         <f>COUNTIF($F$9:$F$33,"Untested")</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D6" s="8">
         <f>COUNTIF($F$9:$F$33,"Blocked")</f>
@@ -9147,18 +9179,18 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="62">
+        <v>24</v>
+      </c>
+      <c r="F6" s="40">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="29"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -9167,10 +9199,10 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -9193,603 +9225,653 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>570</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>190</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="11"/>
+      <c r="F9" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="62">
+        <v>46325</v>
+      </c>
       <c r="H9" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="139.5" customHeight="1">
+      <c r="A10" s="26" t="s">
+        <v>544</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A10" s="28" t="s">
-        <v>571</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="E10" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="62">
+        <v>46325</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="139.5" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>572</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="11"/>
+      <c r="F11" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="62">
+        <v>46325</v>
+      </c>
       <c r="H11" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="139.5" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A12" s="28" t="s">
-        <v>573</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="E12" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="62">
+        <v>46325</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="139.5" customHeight="1">
+      <c r="A13" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A13" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="B13" s="19" t="s">
+      <c r="D13" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="11"/>
+      <c r="F13" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="62">
+        <v>46325</v>
+      </c>
       <c r="H13" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A14" s="28" t="s">
-        <v>575</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="A14" s="26" t="s">
+        <v>548</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="11"/>
+      <c r="F14" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="62">
+        <v>46325</v>
+      </c>
       <c r="H14" s="9" t="s">
-        <v>208</v>
+        <v>671</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A15" s="27" t="s">
-        <v>576</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>209</v>
+      <c r="A15" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>210</v>
+        <v>672</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>211</v>
+        <v>673</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="11"/>
+      <c r="F15" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="62">
+        <v>46325</v>
+      </c>
       <c r="H15" s="9" t="s">
-        <v>212</v>
+        <v>674</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A16" s="28" t="s">
-        <v>577</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E16" s="12" t="s">
+      <c r="A16" s="26" t="s">
+        <v>550</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="11"/>
+      <c r="F16" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="62">
+        <v>46325</v>
+      </c>
       <c r="H16" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>217</v>
+      <c r="A17" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>207</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="11"/>
+      <c r="F17" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="62">
+        <v>46325</v>
+      </c>
       <c r="H17" s="9" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A18" s="28" t="s">
-        <v>579</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E18" s="12" t="s">
+      <c r="A18" s="26" t="s">
+        <v>552</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="F18" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="62">
+        <v>46325</v>
+      </c>
       <c r="H18" s="9" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>580</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>223</v>
+      <c r="A19" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>213</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>224</v>
+        <v>677</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>225</v>
+        <v>678</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="11"/>
+      <c r="F19" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="62">
+        <v>46325</v>
+      </c>
       <c r="H19" s="9" t="s">
-        <v>226</v>
+        <v>679</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>581</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="12" t="s">
+      <c r="A20" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="11"/>
+      <c r="F20" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="62">
+        <v>46325</v>
+      </c>
       <c r="H20" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A21" s="27" t="s">
-        <v>582</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>230</v>
+      <c r="A21" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>217</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="11"/>
+      <c r="F21" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="62">
+        <v>46325</v>
+      </c>
       <c r="H21" s="9" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>583</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22" s="12" t="s">
+      <c r="A22" s="26" t="s">
+        <v>556</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="11"/>
+      <c r="F22" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="62">
+        <v>46325</v>
+      </c>
       <c r="H22" s="9" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>584</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>237</v>
+      <c r="A23" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="11"/>
+      <c r="F23" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="62">
+        <v>46325</v>
+      </c>
       <c r="H23" s="9" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>585</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="A24" s="26" t="s">
+        <v>558</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="11"/>
+      <c r="F24" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="62">
+        <v>46325</v>
+      </c>
       <c r="H24" s="9" t="s">
-        <v>244</v>
+        <v>682</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A25" s="27" t="s">
-        <v>586</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>245</v>
+      <c r="A25" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>229</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="11"/>
+      <c r="F25" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="62">
+        <v>46325</v>
+      </c>
       <c r="H25" s="9" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>587</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="E26" s="12" t="s">
+      <c r="A26" s="26" t="s">
+        <v>560</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="11"/>
+      <c r="F26" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="62">
+        <v>46325</v>
+      </c>
       <c r="H26" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A27" s="27" t="s">
-        <v>588</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>253</v>
+      <c r="A27" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>237</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" s="11"/>
+      <c r="F27" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="62">
+        <v>46325</v>
+      </c>
       <c r="H27" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E28" s="12" t="s">
+      <c r="A28" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" s="11"/>
+      <c r="F28" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="62">
+        <v>46325</v>
+      </c>
       <c r="H28" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>590</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>259</v>
+      <c r="A29" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="11"/>
+      <c r="F29" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="62">
+        <v>46325</v>
+      </c>
       <c r="H29" s="9" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>591</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E30" s="12" t="s">
+      <c r="A30" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" s="11"/>
+      <c r="F30" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="62">
+        <v>46325</v>
+      </c>
       <c r="H30" s="9" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="156" customHeight="1">
-      <c r="A31" s="27" t="s">
-        <v>592</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>267</v>
+      <c r="A31" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>251</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>268</v>
+        <v>683</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" s="11"/>
+      <c r="F31" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="62">
+        <v>46325</v>
+      </c>
       <c r="H31" s="9" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="156" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>593</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E32" s="12" t="s">
+      <c r="A32" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="11"/>
+      <c r="F32" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="62">
+        <v>46325</v>
+      </c>
       <c r="H32" s="9" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A33" s="27" t="s">
-        <v>594</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>275</v>
+      <c r="A33" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>256</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="11"/>
+      <c r="F33" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="62">
+        <v>46325</v>
+      </c>
       <c r="H33" s="9" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -10782,7 +10864,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F9:F33" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F9:F33" xr:uid="{DD1B927F-6CAD-48F5-9888-7BB3C6C3E6E1}">
       <formula1>"Passed,Failed,Untested,Blocked,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10823,43 +10905,43 @@
       <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="7" t="s">
@@ -10877,24 +10959,24 @@
       <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="8">
         <f>COUNTIF($F$9:$F$33,"Passed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF($F$9:$F$33,"Failed")</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C6" s="8">
         <f>COUNTIF($F$9:$F$33,"Untested")</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D6" s="8">
         <f>COUNTIF($F$9:$F$33,"Blocked")</f>
@@ -10902,14 +10984,14 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTIF($F$9:$F$33,"Skipped")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="62">
+        <v>1</v>
+      </c>
+      <c r="F6" s="40">
         <f>COUNTA(A9:A33)</f>
         <v>25</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -10949,602 +11031,652 @@
     </row>
     <row r="9" spans="1:8" ht="139.5" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="64">
+        <v>46325</v>
+      </c>
       <c r="H9" s="9" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="11"/>
+      <c r="A10" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="64">
+        <v>46325</v>
+      </c>
       <c r="H10" s="9" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="139.5" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>288</v>
+        <v>686</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="64">
+        <v>46325</v>
+      </c>
       <c r="H11" s="9" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>598</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="11"/>
+      <c r="A12" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="64">
+        <v>46325</v>
+      </c>
       <c r="H12" s="9" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="139.5" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>293</v>
+        <v>687</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>294</v>
+        <v>688</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="64">
+        <v>46325</v>
+      </c>
       <c r="H13" s="9" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>600</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="11"/>
+      <c r="A14" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="64">
+        <v>46325</v>
+      </c>
       <c r="H14" s="9" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="139.5" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="64">
+        <v>46325</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="9" t="s">
-        <v>303</v>
-      </c>
     </row>
     <row r="16" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A16" s="12" t="s">
-        <v>602</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E16" s="12" t="s">
+      <c r="A16" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="64">
+        <v>46325</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="9" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="139.5" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="64">
+        <v>46325</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="9" t="s">
-        <v>303</v>
-      </c>
     </row>
     <row r="18" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>604</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="A18" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="64">
+        <v>46325</v>
+      </c>
       <c r="H18" s="9" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="139.5" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="64">
+        <v>46325</v>
+      </c>
       <c r="H19" s="9" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="11"/>
+      <c r="A20" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="64">
+        <v>46325</v>
+      </c>
       <c r="H20" s="9" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="139.5" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>607</v>
+        <v>580</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="64">
+        <v>46325</v>
+      </c>
       <c r="H21" s="9" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>608</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="11"/>
+      <c r="A22" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="64">
+        <v>46325</v>
+      </c>
       <c r="H22" s="9" t="s">
-        <v>329</v>
+        <v>690</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="139.5" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="64">
+        <v>46325</v>
+      </c>
       <c r="H23" s="9" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A24" s="12" t="s">
-        <v>610</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="11"/>
+      <c r="A24" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="64">
+        <v>46325</v>
+      </c>
       <c r="H24" s="9" t="s">
-        <v>337</v>
+        <v>691</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="139.5" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="64">
+        <v>46325</v>
+      </c>
       <c r="H25" s="9" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="141.75" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="11"/>
+      <c r="A26" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F26" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="64">
+        <v>46325</v>
+      </c>
       <c r="H26" s="9" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="141.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="64">
+        <v>46325</v>
+      </c>
       <c r="H27" s="9" t="s">
-        <v>347</v>
+        <v>692</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A28" s="12" t="s">
-        <v>614</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G28" s="11"/>
+      <c r="A28" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="64">
+        <v>46325</v>
+      </c>
       <c r="H28" s="9" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="139.5" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>352</v>
+        <v>694</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F29" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="64">
+        <v>46325</v>
+      </c>
       <c r="H29" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A30" s="12" t="s">
-        <v>616</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" s="11"/>
+      <c r="A30" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F30" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" s="64">
+        <v>46325</v>
+      </c>
       <c r="H30" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="139.5" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F31" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="64">
+        <v>46325</v>
+      </c>
       <c r="H31" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="139.5" customHeight="1">
-      <c r="A32" s="12" t="s">
-        <v>618</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="11"/>
+      <c r="A32" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F32" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="64">
+        <v>46325</v>
+      </c>
       <c r="H32" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="139.5" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="11"/>
+        <v>262</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="64">
+        <v>46325</v>
+      </c>
       <c r="H33" s="9" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1"/>
@@ -12537,7 +12669,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F9:F33" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F9:F33" xr:uid="{094D1D0D-D2FA-4E32-B185-E989067C388A}">
       <formula1>"Passed,Failed,Untested,Blocked,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12568,14 +12700,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="57" t="s">
-        <v>367</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="A2" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -12607,22 +12739,22 @@
     </row>
     <row r="5" spans="1:6" ht="99.6" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>492</v>
+        <v>341</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>465</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="109.5" customHeight="1">
@@ -12630,319 +12762,319 @@
         <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="109.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="109.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>385</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="109.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="109.5" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="109.5" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>624</v>
+        <v>597</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="109.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="114.6" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="109.5" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="109.5" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>628</v>
+        <v>601</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="109.5" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="109.5" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>427</v>
+        <v>400</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="115.2" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="109.5" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="109.5" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="109.5" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
@@ -12969,13 +13101,13 @@
     </row>
     <row r="24" spans="1:6" ht="69.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="B24" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="B24" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>460</v>
+      <c r="C24" s="12" t="s">
+        <v>433</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -12983,13 +13115,13 @@
     </row>
     <row r="25" spans="1:6" ht="69.75" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>452</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>461</v>
+        <v>424</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>425</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -12997,13 +13129,13 @@
     </row>
     <row r="26" spans="1:6" ht="69.75" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>462</v>
+        <v>426</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>435</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -13011,13 +13143,13 @@
     </row>
     <row r="27" spans="1:6" ht="69.75" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>463</v>
+        <v>428</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>429</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>436</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -13025,27 +13157,27 @@
     </row>
     <row r="28" spans="1:6" ht="69.75" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>458</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>464</v>
+        <v>430</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>431</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>437</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" ht="69.75" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>466</v>
+      <c r="A29" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>439</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -14033,14 +14165,14 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="42" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -14075,19 +14207,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>498</v>
+        <v>470</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>471</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>678</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="150" customHeight="1">
@@ -14095,19 +14227,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="150" customHeight="1">
@@ -14115,19 +14247,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>680</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="150" customHeight="1">
@@ -14135,19 +14267,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="150" customHeight="1">
@@ -14155,19 +14287,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="150" customHeight="1">
@@ -14175,19 +14307,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="150" customHeight="1">
@@ -14195,19 +14327,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="150" customHeight="1">
@@ -14215,19 +14347,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>634</v>
+        <v>607</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="150" customHeight="1">
@@ -14235,19 +14367,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>635</v>
+        <v>608</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="150" customHeight="1">
@@ -14255,19 +14387,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="150" customHeight="1">
@@ -14275,19 +14407,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>536</v>
+        <v>509</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>685</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="150" customHeight="1">
@@ -14295,19 +14427,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>538</v>
+        <v>511</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>539</v>
+        <v>512</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>687</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="150" customHeight="1">
@@ -14315,19 +14447,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15363,16 +15495,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="42" customHeight="1">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="1"/>
@@ -15385,64 +15517,64 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="40" t="str">
+      <c r="C3" s="36"/>
+      <c r="D3" s="48" t="str">
         <f>Cover!C4</f>
         <v>OrangeHRM Recruitment</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="40" t="str">
+      <c r="C4" s="36"/>
+      <c r="D4" s="48" t="str">
         <f>Cover!C6</f>
         <v>Group01_23130299_NguyenVanThang</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42" t="s">
-        <v>692</v>
-      </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="63">
+      <c r="C5" s="36"/>
+      <c r="D5" s="57" t="s">
+        <v>665</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="58">
         <v>46318.496458333335</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42" t="s">
-        <v>693</v>
-      </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="57" t="s">
+        <v>666</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="1"/>
@@ -15535,11 +15667,11 @@
       </c>
       <c r="E11" s="4">
         <f>RECRUIT_CAND!B6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4">
         <f>RECRUIT_CAND!C6</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4">
         <f>RECRUIT_CAND!D6</f>
@@ -15547,7 +15679,7 @@
       </c>
       <c r="H11" s="4">
         <f>RECRUIT_CAND!E6</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I11" s="4">
         <f>RECRUIT_CAND!F6</f>
@@ -15563,15 +15695,15 @@
       </c>
       <c r="D12" s="4">
         <f>RECRUIT_FLOW!A6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
         <f>RECRUIT_FLOW!B6</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F12" s="4">
         <f>RECRUIT_FLOW!C6</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4">
         <f>RECRUIT_FLOW!D6</f>
@@ -15579,7 +15711,7 @@
       </c>
       <c r="H12" s="4">
         <f>RECRUIT_FLOW!E6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4">
         <f>RECRUIT_FLOW!F6</f>
@@ -15597,31 +15729,31 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="13">
+      <c r="C14" s="39"/>
+      <c r="D14" s="11">
         <f t="shared" ref="D14:I14" si="0">SUM(D10:D12)</f>
-        <v>23</v>
-      </c>
-      <c r="E14" s="13">
+        <v>24</v>
+      </c>
+      <c r="E14" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F14" s="13">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G14" s="13">
+        <v>26</v>
+      </c>
+      <c r="F14" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="13">
+      <c r="G14" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="13">
+      <c r="H14" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I14" s="11">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
@@ -15647,31 +15779,31 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="46">
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="60">
         <f>IF(I14=0,"",(D14+E14)/I14)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F17" s="41"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F17" s="36"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="46">
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="60">
         <f>IF(D14+E14=0,"Chưa thực thi",D14/(D14+E14))</f>
-        <v>0.92</v>
-      </c>
-      <c r="F18" s="41"/>
+        <v>0.48</v>
+      </c>
+      <c r="F18" s="36"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -15687,16 +15819,16 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
     </row>
     <row r="21" spans="2:9" ht="15.75" customHeight="1">
       <c r="B21" s="1"/>
@@ -15709,16 +15841,16 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
     </row>
     <row r="23" spans="2:9" ht="15.75" customHeight="1">
       <c r="B23" s="1"/>
